--- a/news_daily/2026-10-16.xlsx
+++ b/news_daily/2026-10-16.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH61"/>
+  <dimension ref="A1:BL61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1011,6 +1027,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1177,6 +1197,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1351,6 +1375,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1525,6 +1553,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1699,6 +1731,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1865,6 +1901,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2031,6 +2071,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2205,6 +2249,10 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2379,6 +2427,10 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2545,6 +2597,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2719,6 +2775,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2885,6 +2945,10 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3059,6 +3123,10 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr"/>
+      <c r="BL14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3233,6 +3301,10 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3407,6 +3479,10 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3581,6 +3657,10 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3747,6 +3827,10 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3913,6 +3997,10 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4087,6 +4175,10 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4261,6 +4353,10 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4435,6 +4531,10 @@
         </is>
       </c>
       <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BJ22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr"/>
+      <c r="BL22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4609,6 +4709,10 @@
         </is>
       </c>
       <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BI23" s="3" t="inlineStr"/>
+      <c r="BJ23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr"/>
+      <c r="BL23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4783,6 +4887,10 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr"/>
+      <c r="BL24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4949,6 +5057,10 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5123,6 +5235,10 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -5173,13 +5289,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -5232,7 +5352,11 @@
         </is>
       </c>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>664e09f00be14046869d9224b6a26606</t>
+        </is>
+      </c>
       <c r="AC27" s="4" t="inlineStr">
         <is>
           <t>9beadf3792e846e19630abb4</t>
@@ -5253,7 +5377,11 @@
       <c r="AL27" s="4" t="inlineStr"/>
       <c r="AM27" s="4" t="inlineStr"/>
       <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
+      <c r="AO27" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="4" t="inlineStr"/>
       <c r="AQ27" s="4" t="inlineStr"/>
       <c r="AR27" s="4" t="inlineStr"/>
@@ -5297,6 +5425,18 @@
         </is>
       </c>
       <c r="BH27" s="4" t="inlineStr"/>
+      <c r="BI27" s="4" t="inlineStr"/>
+      <c r="BJ27" s="4" t="inlineStr"/>
+      <c r="BK27" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5463,6 +5603,10 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5629,6 +5773,10 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5803,6 +5951,10 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr"/>
+      <c r="BL30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5973,6 +6125,10 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr"/>
+      <c r="BL31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6139,6 +6295,10 @@
         </is>
       </c>
       <c r="BH32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr"/>
+      <c r="BJ32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr"/>
+      <c r="BL32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6305,6 +6465,10 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr"/>
+      <c r="BL33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6479,6 +6643,10 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BJ34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr"/>
+      <c r="BL34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6645,6 +6813,10 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BJ35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr"/>
+      <c r="BL35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -6819,350 +6991,410 @@
         </is>
       </c>
       <c r="BH36" s="3" t="inlineStr"/>
+      <c r="BI36" s="3" t="inlineStr"/>
+      <c r="BJ36" s="3" t="inlineStr"/>
+      <c r="BK36" s="3" t="inlineStr"/>
+      <c r="BL36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>NEE</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>NextEra Energy, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T03:13:04+08:00</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>NextEra Energy (NEE) Proposes Legal Settlement, Is It Still Undervalued?</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>'-0.119</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPVl9TTzhhQ3YyZXhfdWVNTTczZTVxbHV6V2c4cjBlQ1JfYW9oM0hJN0xrM2QxTElac0RBaDV4VEQxbFc4RERfclZwQm1xck1qdWtrNkplYWw4cU92N1V2d19zOFNsbm9DOWh1UzZEdUk5aC0yeURzTDVIVWhuem0zTVV6Y0l6V1RTRHhfeHg4YUVqR3AyLUNQUGJYQWFERWFiWnAxWE92emw0MnFzMksyVklTMUFWM3VEZlhBTkt1OUFMb05FZ0JDUDdBc9IB0AFBVV95cUxOTUp6THZvMEczYW9GZGdObEVoNnlnOFhmWDBTVmFnZnIwUU5CUERVVEFxdGY1QnVWcTVyZzdmQmFuZUhXVUhLWXVsZXpVUUFpS04yNnBpSHFCY1g1MnNyX0VEbGdKSkpDcjNTWElyY3gwVTl1MTBpNlFudEpvaktpdGg5MHhjTnF1Mi1CX1J6ckEtWUl0T3I5U0NCX21Cc2V6YnVuZkNCZFl1UG1KZGdlaDNENk5hc01ZNUJPa1pQdEtqYTVPTmJ5bC1zTTRJazZk?oc=5</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>NextEra Energy（NEE）提出法律和解，其價值是否仍被低估？</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>7cab6344b1154341b9e8c15840478a4d</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>18cbfc1204e0da57cb84360d</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>0512a9b31af1946f9e403ace</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+      <c r="AK37" s="2" t="inlineStr"/>
+      <c r="AL37" s="2" t="inlineStr"/>
+      <c r="AM37" s="2" t="inlineStr"/>
+      <c r="AN37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>'-0.119</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr"/>
-      <c r="Q37" s="4" t="inlineStr"/>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPVl9TTzhhQ3YyZXhfdWVNTTczZTVxbHV6V2c4cjBlQ1JfYW9oM0hJN0xrM2QxTElac0RBaDV4VEQxbFc4RERfclZwQm1xck1qdWtrNkplYWw4cU92N1V2d19zOFNsbm9DOWh1UzZEdUk5aC0yeURzTDVIVWhuem0zTVV6Y0l6V1RTRHhfeHg4YUVqR3AyLUNQUGJYQWFERWFiWnAxWE92emw0MnFzMksyVklTMUFWM3VEZlhBTkt1OUFMb05FZ0JDUDdBc9IB0AFBVV95cUxOTUp6THZvMEczYW9GZGdObEVoNnlnOFhmWDBTVmFnZnIwUU5CUERVVEFxdGY1QnVWcTVyZzdmQmFuZUhXVUhLWXVsZXpVUUFpS04yNnBpSHFCY1g1MnNyX0VEbGdKSkpDcjNTWElyY3gwVTl1MTBpNlFudEpvaktpdGg5MHhjTnF1Mi1CX1J6ckEtWUl0T3I5U0NCX21Cc2V6YnVuZkNCZFl1UG1KZGdlaDNENk5hc01ZNUJPa1pQdEtqYTVPTmJ5bC1zTTRJazZk?oc=5</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="inlineStr">
-        <is>
-          <t>NextEra Energy（NEE）提出法律和解，其價值是否仍被低估？</t>
-        </is>
-      </c>
-      <c r="X37" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y37" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z37" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="inlineStr"/>
-      <c r="AC37" s="4" t="inlineStr">
-        <is>
-          <t>18cbfc1204e0da57cb84360d</t>
-        </is>
-      </c>
-      <c r="AD37" s="4" t="inlineStr">
-        <is>
-          <t>0512a9b31af1946f9e403ace</t>
-        </is>
-      </c>
-      <c r="AE37" s="4" t="inlineStr"/>
-      <c r="AF37" s="4" t="inlineStr"/>
-      <c r="AG37" s="4" t="inlineStr"/>
-      <c r="AH37" s="4" t="inlineStr"/>
-      <c r="AI37" s="4" t="inlineStr"/>
-      <c r="AJ37" s="4" t="inlineStr"/>
-      <c r="AK37" s="4" t="inlineStr"/>
-      <c r="AL37" s="4" t="inlineStr"/>
-      <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="inlineStr"/>
-      <c r="AP37" s="4" t="inlineStr"/>
-      <c r="AQ37" s="4" t="inlineStr"/>
-      <c r="AR37" s="4" t="inlineStr"/>
-      <c r="AS37" s="4" t="inlineStr"/>
-      <c r="AT37" s="4" t="inlineStr"/>
-      <c r="AU37" s="4" t="inlineStr"/>
-      <c r="AV37" s="4" t="inlineStr"/>
-      <c r="AW37" s="4" t="inlineStr">
+      <c r="AP37" s="2" t="inlineStr"/>
+      <c r="AQ37" s="2" t="inlineStr"/>
+      <c r="AR37" s="2" t="inlineStr"/>
+      <c r="AS37" s="2" t="inlineStr"/>
+      <c r="AT37" s="2" t="inlineStr"/>
+      <c r="AU37" s="2" t="inlineStr"/>
+      <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX37" s="4" t="inlineStr"/>
-      <c r="AY37" s="4" t="inlineStr"/>
-      <c r="AZ37" s="4" t="inlineStr"/>
-      <c r="BA37" s="4" t="inlineStr"/>
-      <c r="BB37" s="4" t="inlineStr">
+      <c r="AX37" s="2" t="inlineStr"/>
+      <c r="AY37" s="2" t="inlineStr"/>
+      <c r="AZ37" s="2" t="inlineStr"/>
+      <c r="BA37" s="2" t="inlineStr"/>
+      <c r="BB37" s="2" t="inlineStr">
         <is>
           <t>NEE</t>
         </is>
       </c>
-      <c r="BC37" s="4" t="inlineStr">
+      <c r="BC37" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD37" s="4" t="inlineStr"/>
-      <c r="BE37" s="4" t="inlineStr">
+      <c r="BD37" s="2" t="inlineStr"/>
+      <c r="BE37" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF37" s="4" t="inlineStr">
+      <c r="BF37" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG37" s="4" t="inlineStr">
+      <c r="BG37" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH37" s="4" t="inlineStr"/>
+      <c r="BH37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>CoreWeave, Inc.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>2026-10-16T02:11:47+08:00</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>CoreWeave Credit Risk Hits Record, Pricing 60% Odds of Default</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>CDS利差擴大／信用風險升高</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOQ3cxbDJzTDhpNzNXR3JBZVI4OXVkLUQzcUNSUUJHam5BU1NuRUtNZUV0RXBNVlQ3bGFBV2ZoOXN3dU9HLWlockI5S1ZLZzVwMDBqTFVSTjhWcWxmeENjUUk0TGJrOUZ2OC1SNU9jRG85cnNEMDg4TmtXWHU2ZV85d3FBVUo0SG9ldmx4RjNFaEVvTnlSd1lOMndGcXhfTEwyYVJLNWZpdHpxeGNxLWVj?oc=5</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>CDS_SPREAD_WIDENING</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>afa3e19288624017801f27d8504d8772</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>a997bfc9e524bb7bf0e90552</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>bb52f9b5bbfeed84bb46932d</t>
+        </is>
+      </c>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOQ3cxbDJzTDhpNzNXR3JBZVI4OXVkLUQzcUNSUUJHam5BU1NuRUtNZUV0RXBNVlQ3bGFBV2ZoOXN3dU9HLWlockI5S1ZLZzVwMDBqTFVSTjhWcWxmeENjUUk0TGJrOUZ2OC1SNU9jRG85cnNEMDg4TmtXWHU2ZV85d3FBVUo0SG9ldmx4RjNFaEVvTnlSd1lOMndGcXhfTEwyYVJLNWZpdHpxeGNxLWVj?oc=5</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
-      <c r="X38" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z38" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA38" s="5" t="inlineStr"/>
-      <c r="AB38" s="5" t="inlineStr"/>
-      <c r="AC38" s="5" t="inlineStr">
-        <is>
-          <t>a997bfc9e524bb7bf0e90552</t>
-        </is>
-      </c>
-      <c r="AD38" s="5" t="inlineStr">
-        <is>
-          <t>bb52f9b5bbfeed84bb46932d</t>
-        </is>
-      </c>
-      <c r="AE38" s="5" t="inlineStr"/>
-      <c r="AF38" s="5" t="inlineStr"/>
-      <c r="AG38" s="5" t="inlineStr"/>
-      <c r="AH38" s="5" t="inlineStr"/>
-      <c r="AI38" s="5" t="inlineStr"/>
-      <c r="AJ38" s="5" t="inlineStr"/>
-      <c r="AK38" s="5" t="inlineStr"/>
-      <c r="AL38" s="5" t="inlineStr"/>
-      <c r="AM38" s="5" t="inlineStr"/>
-      <c r="AN38" s="5" t="inlineStr"/>
-      <c r="AO38" s="5" t="inlineStr"/>
-      <c r="AP38" s="5" t="inlineStr"/>
-      <c r="AQ38" s="5" t="inlineStr"/>
-      <c r="AR38" s="5" t="inlineStr"/>
-      <c r="AS38" s="5" t="inlineStr"/>
-      <c r="AT38" s="5" t="inlineStr"/>
-      <c r="AU38" s="5" t="inlineStr"/>
-      <c r="AV38" s="5" t="inlineStr"/>
-      <c r="AW38" s="5" t="inlineStr">
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr"/>
+      <c r="AS38" s="3" t="inlineStr"/>
+      <c r="AT38" s="3" t="inlineStr"/>
+      <c r="AU38" s="3" t="inlineStr"/>
+      <c r="AV38" s="3" t="inlineStr"/>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX38" s="5" t="inlineStr"/>
-      <c r="AY38" s="5" t="inlineStr"/>
-      <c r="AZ38" s="5" t="inlineStr"/>
-      <c r="BA38" s="5" t="inlineStr"/>
-      <c r="BB38" s="5" t="inlineStr">
+      <c r="AX38" s="3" t="inlineStr"/>
+      <c r="AY38" s="3" t="inlineStr"/>
+      <c r="AZ38" s="3" t="inlineStr"/>
+      <c r="BA38" s="3" t="inlineStr"/>
+      <c r="BB38" s="3" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="BC38" s="5" t="inlineStr">
+      <c r="BC38" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD38" s="5" t="inlineStr"/>
-      <c r="BE38" s="5" t="inlineStr">
+      <c r="BD38" s="3" t="inlineStr"/>
+      <c r="BE38" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF38" s="5" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG38" s="5" t="inlineStr">
+      <c r="BG38" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH38" s="5" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr"/>
+      <c r="BI38" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ38" s="3" t="inlineStr"/>
+      <c r="BK38" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7337,180 +7569,212 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BJ39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr"/>
+      <c r="BL39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T01:50:13+08:00</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Starbucks/Chipotle merge rumors, True Food’s bankruptcy, and Uber’s big acquisition</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>'-0.646</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQV0N6TUpTWTVrNUplM01qUVdubU9xSWNsenU3NDdoM0lkUlFOTC1Qb0xDYWRkaEY2dlkzVXJxa19KS0lJZGs3UXhkMDlzY1ZLR1NUQmdiUDVzN3NUV2NkT3BCamNZTTBXNU9fNnpERHFmTkZiZUdBeDY0NXFkYjYxQWdocGNJdkpkTXpkcWdHV3g5eTYtZVktODRFamdXTFVtck5xWTZLYl9VU0VRTllOakZMM19VYmtG?oc=5</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Nation’s Restaurant News</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>星巴克/Chipotle 合併傳聞、True Food 破產、Uber 大舉收購</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>40a4abe5dc9544fe98c321c36082433b</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2548b4914d2ed2563e69c8e2</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>ce135397e6d5382cbe073479</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="inlineStr"/>
+      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>'-0.646</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQV0N6TUpTWTVrNUplM01qUVdubU9xSWNsenU3NDdoM0lkUlFOTC1Qb0xDYWRkaEY2dlkzVXJxa19KS0lJZGs3UXhkMDlzY1ZLR1NUQmdiUDVzN3NUV2NkT3BCamNZTTBXNU9fNnpERHFmTkZiZUdBeDY0NXFkYjYxQWdocGNJdkpkTXpkcWdHV3g5eTYtZVktODRFamdXTFVtck5xWTZLYl9VU0VRTllOakZMM19VYmtG?oc=5</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>Nation’s Restaurant News</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr">
-        <is>
-          <t>星巴克/Chipotle 合併傳聞、True Food 破產、Uber 大舉收購</t>
-        </is>
-      </c>
-      <c r="X40" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y40" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z40" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA40" s="5" t="inlineStr"/>
-      <c r="AB40" s="5" t="inlineStr"/>
-      <c r="AC40" s="5" t="inlineStr">
-        <is>
-          <t>2548b4914d2ed2563e69c8e2</t>
-        </is>
-      </c>
-      <c r="AD40" s="5" t="inlineStr">
-        <is>
-          <t>ce135397e6d5382cbe073479</t>
-        </is>
-      </c>
-      <c r="AE40" s="5" t="inlineStr"/>
-      <c r="AF40" s="5" t="inlineStr"/>
-      <c r="AG40" s="5" t="inlineStr"/>
-      <c r="AH40" s="5" t="inlineStr"/>
-      <c r="AI40" s="5" t="inlineStr"/>
-      <c r="AJ40" s="5" t="inlineStr"/>
-      <c r="AK40" s="5" t="inlineStr"/>
-      <c r="AL40" s="5" t="inlineStr"/>
-      <c r="AM40" s="5" t="inlineStr"/>
-      <c r="AN40" s="5" t="inlineStr"/>
-      <c r="AO40" s="5" t="inlineStr"/>
-      <c r="AP40" s="5" t="inlineStr"/>
-      <c r="AQ40" s="5" t="inlineStr"/>
-      <c r="AR40" s="5" t="inlineStr"/>
-      <c r="AS40" s="5" t="inlineStr"/>
-      <c r="AT40" s="5" t="inlineStr"/>
-      <c r="AU40" s="5" t="inlineStr"/>
-      <c r="AV40" s="5" t="inlineStr"/>
-      <c r="AW40" s="5" t="inlineStr">
+      <c r="AP40" s="2" t="inlineStr"/>
+      <c r="AQ40" s="2" t="inlineStr"/>
+      <c r="AR40" s="2" t="inlineStr"/>
+      <c r="AS40" s="2" t="inlineStr"/>
+      <c r="AT40" s="2" t="inlineStr"/>
+      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX40" s="5" t="inlineStr"/>
-      <c r="AY40" s="5" t="inlineStr"/>
-      <c r="AZ40" s="5" t="inlineStr"/>
-      <c r="BA40" s="5" t="inlineStr"/>
-      <c r="BB40" s="5" t="inlineStr">
+      <c r="AX40" s="2" t="inlineStr"/>
+      <c r="AY40" s="2" t="inlineStr"/>
+      <c r="AZ40" s="2" t="inlineStr"/>
+      <c r="BA40" s="2" t="inlineStr"/>
+      <c r="BB40" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC40" s="5" t="inlineStr">
+      <c r="BC40" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD40" s="5" t="inlineStr"/>
-      <c r="BE40" s="5" t="inlineStr">
+      <c r="BD40" s="2" t="inlineStr"/>
+      <c r="BE40" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF40" s="5" t="inlineStr">
+      <c r="BF40" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG40" s="5" t="inlineStr">
+      <c r="BG40" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH40" s="5" t="inlineStr"/>
+      <c r="BH40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7685,6 +7949,10 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BJ41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr"/>
+      <c r="BL41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7859,6 +8127,10 @@
         </is>
       </c>
       <c r="BH42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr"/>
+      <c r="BJ42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr"/>
+      <c r="BL42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -8033,6 +8305,10 @@
         </is>
       </c>
       <c r="BH43" s="3" t="inlineStr"/>
+      <c r="BI43" s="3" t="inlineStr"/>
+      <c r="BJ43" s="3" t="inlineStr"/>
+      <c r="BK43" s="3" t="inlineStr"/>
+      <c r="BL43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -8207,6 +8483,10 @@
         </is>
       </c>
       <c r="BH44" s="3" t="inlineStr"/>
+      <c r="BI44" s="3" t="inlineStr"/>
+      <c r="BJ44" s="3" t="inlineStr"/>
+      <c r="BK44" s="3" t="inlineStr"/>
+      <c r="BL44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8373,6 +8653,10 @@
         </is>
       </c>
       <c r="BH45" s="3" t="inlineStr"/>
+      <c r="BI45" s="3" t="inlineStr"/>
+      <c r="BJ45" s="3" t="inlineStr"/>
+      <c r="BK45" s="3" t="inlineStr"/>
+      <c r="BL45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -8413,7 +8697,7 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -8423,13 +8707,17 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -8473,7 +8761,7 @@
       </c>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z46" s="4" t="inlineStr">
@@ -8482,7 +8770,11 @@
         </is>
       </c>
       <c r="AA46" s="4" t="inlineStr"/>
-      <c r="AB46" s="4" t="inlineStr"/>
+      <c r="AB46" s="4" t="inlineStr">
+        <is>
+          <t>8db6f3649abe4d398280b8ab90bf2681</t>
+        </is>
+      </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
           <t>ada93744837e92947d202f3e</t>
@@ -8503,7 +8795,11 @@
       <c r="AL46" s="4" t="inlineStr"/>
       <c r="AM46" s="4" t="inlineStr"/>
       <c r="AN46" s="4" t="inlineStr"/>
-      <c r="AO46" s="4" t="inlineStr"/>
+      <c r="AO46" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="4" t="inlineStr"/>
       <c r="AQ46" s="4" t="inlineStr"/>
       <c r="AR46" s="4" t="inlineStr"/>
@@ -8547,6 +8843,22 @@
         </is>
       </c>
       <c r="BH46" s="4" t="inlineStr"/>
+      <c r="BI46" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ46" s="4" t="inlineStr"/>
+      <c r="BK46" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8721,6 +9033,10 @@
         </is>
       </c>
       <c r="BH47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr"/>
+      <c r="BJ47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr"/>
+      <c r="BL47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -8887,176 +9203,208 @@
         </is>
       </c>
       <c r="BH48" s="3" t="inlineStr"/>
+      <c r="BI48" s="3" t="inlineStr"/>
+      <c r="BJ48" s="3" t="inlineStr"/>
+      <c r="BK48" s="3" t="inlineStr"/>
+      <c r="BL48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>CoreWeave, Inc.</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>2026-10-16T00:52:16+08:00</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>CoreWeave credit default swaps hit distress levels as investors sour on AI debt</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>CDS利差擴大／信用風險升高</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr"/>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>CDS_SPREAD_WIDENING</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>9a2cf57383d049b595007302e6da1711</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>15701a5080a3de1ba6257ef1</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr">
+        <is>
+          <t>0040b1fc371664e2cde9c86e</t>
+        </is>
+      </c>
+      <c r="AE49" s="3" t="inlineStr"/>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr"/>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr"/>
+      <c r="AM49" s="3" t="inlineStr"/>
+      <c r="AN49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
-        </is>
-      </c>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
-      <c r="X49" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y49" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z49" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA49" s="5" t="inlineStr"/>
-      <c r="AB49" s="5" t="inlineStr"/>
-      <c r="AC49" s="5" t="inlineStr">
-        <is>
-          <t>15701a5080a3de1ba6257ef1</t>
-        </is>
-      </c>
-      <c r="AD49" s="5" t="inlineStr">
-        <is>
-          <t>0040b1fc371664e2cde9c86e</t>
-        </is>
-      </c>
-      <c r="AE49" s="5" t="inlineStr"/>
-      <c r="AF49" s="5" t="inlineStr"/>
-      <c r="AG49" s="5" t="inlineStr"/>
-      <c r="AH49" s="5" t="inlineStr"/>
-      <c r="AI49" s="5" t="inlineStr"/>
-      <c r="AJ49" s="5" t="inlineStr"/>
-      <c r="AK49" s="5" t="inlineStr"/>
-      <c r="AL49" s="5" t="inlineStr"/>
-      <c r="AM49" s="5" t="inlineStr"/>
-      <c r="AN49" s="5" t="inlineStr"/>
-      <c r="AO49" s="5" t="inlineStr"/>
-      <c r="AP49" s="5" t="inlineStr"/>
-      <c r="AQ49" s="5" t="inlineStr"/>
-      <c r="AR49" s="5" t="inlineStr"/>
-      <c r="AS49" s="5" t="inlineStr"/>
-      <c r="AT49" s="5" t="inlineStr"/>
-      <c r="AU49" s="5" t="inlineStr"/>
-      <c r="AV49" s="5" t="inlineStr"/>
-      <c r="AW49" s="5" t="inlineStr">
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr"/>
+      <c r="AS49" s="3" t="inlineStr"/>
+      <c r="AT49" s="3" t="inlineStr"/>
+      <c r="AU49" s="3" t="inlineStr"/>
+      <c r="AV49" s="3" t="inlineStr"/>
+      <c r="AW49" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX49" s="5" t="inlineStr"/>
-      <c r="AY49" s="5" t="inlineStr"/>
-      <c r="AZ49" s="5" t="inlineStr"/>
-      <c r="BA49" s="5" t="inlineStr"/>
-      <c r="BB49" s="5" t="inlineStr">
+      <c r="AX49" s="3" t="inlineStr"/>
+      <c r="AY49" s="3" t="inlineStr"/>
+      <c r="AZ49" s="3" t="inlineStr"/>
+      <c r="BA49" s="3" t="inlineStr"/>
+      <c r="BB49" s="3" t="inlineStr">
         <is>
           <t>CRWV</t>
         </is>
       </c>
-      <c r="BC49" s="5" t="inlineStr">
+      <c r="BC49" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD49" s="5" t="inlineStr"/>
-      <c r="BE49" s="5" t="inlineStr">
+      <c r="BD49" s="3" t="inlineStr"/>
+      <c r="BE49" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BG49" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH49" s="5" t="inlineStr"/>
+      <c r="BH49" s="3" t="inlineStr"/>
+      <c r="BI49" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ49" s="3" t="inlineStr"/>
+      <c r="BK49" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9231,180 +9579,212 @@
         </is>
       </c>
       <c r="BH50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr"/>
+      <c r="BJ50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr"/>
+      <c r="BL50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>CMS Energy Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T00:30:25+08:00</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FTC to Healthcare Providers: CMS Price Transparency Compliance Is Not Safe Harbor</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>'-0.583</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbS1rWDVwMExxOHVRaU5Gbk11NmVZT3FzcnFoMFJ3MDQzSmVYLS1UZnlTV3A1bVBpQXltTldjNV9Wd2xoUC0wWkhYdTVwMU9Za3N3V3U4X0FYb3g3WHFCMjRvUVg4RXBFS1ZLZXJUM3FYZThPUXQ3bmdLbGZNZ0M4WWRMRVJqZUpQd2o5LVJvSVlSZFhuMVJ4WDkzYnhiM0VEbVVPS0RFM1lrZjZmQ2FWd0hXeVd5R0pyVzRfNlpUMUxMQTh4NkNLUDR2ZDdXRjloTkFQZmNGTzBSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>McGuireWoods</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>FTC 致醫療保健提供者：CMS 價格透明度合規並非安全港</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>88d8f93c453b411691f04c833f68cc02</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>b57f1ae761039b095c1a3b9f</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>bacf34c1ecdf56c4b714001b</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+      <c r="AK51" s="2" t="inlineStr"/>
+      <c r="AL51" s="2" t="inlineStr"/>
+      <c r="AM51" s="2" t="inlineStr"/>
+      <c r="AN51" s="2" t="inlineStr"/>
+      <c r="AO51" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O51" s="4" t="inlineStr">
-        <is>
-          <t>'-0.583</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="4" t="inlineStr"/>
-      <c r="R51" s="4" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U51" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbS1rWDVwMExxOHVRaU5Gbk11NmVZT3FzcnFoMFJ3MDQzSmVYLS1UZnlTV3A1bVBpQXltTldjNV9Wd2xoUC0wWkhYdTVwMU9Za3N3V3U4X0FYb3g3WHFCMjRvUVg4RXBFS1ZLZXJUM3FYZThPUXQ3bmdLbGZNZ0M4WWRMRVJqZUpQd2o5LVJvSVlSZFhuMVJ4WDkzYnhiM0VEbVVPS0RFM1lrZjZmQ2FWd0hXeVd5R0pyVzRfNlpUMUxMQTh4NkNLUDR2ZDdXRjloTkFQZmNGTzBSQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V51" s="4" t="inlineStr">
-        <is>
-          <t>McGuireWoods</t>
-        </is>
-      </c>
-      <c r="W51" s="4" t="inlineStr">
-        <is>
-          <t>FTC 致醫療保健提供者：CMS 價格透明度合規並非安全港</t>
-        </is>
-      </c>
-      <c r="X51" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y51" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z51" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA51" s="4" t="inlineStr"/>
-      <c r="AB51" s="4" t="inlineStr"/>
-      <c r="AC51" s="4" t="inlineStr">
-        <is>
-          <t>b57f1ae761039b095c1a3b9f</t>
-        </is>
-      </c>
-      <c r="AD51" s="4" t="inlineStr">
-        <is>
-          <t>bacf34c1ecdf56c4b714001b</t>
-        </is>
-      </c>
-      <c r="AE51" s="4" t="inlineStr"/>
-      <c r="AF51" s="4" t="inlineStr"/>
-      <c r="AG51" s="4" t="inlineStr"/>
-      <c r="AH51" s="4" t="inlineStr"/>
-      <c r="AI51" s="4" t="inlineStr"/>
-      <c r="AJ51" s="4" t="inlineStr"/>
-      <c r="AK51" s="4" t="inlineStr"/>
-      <c r="AL51" s="4" t="inlineStr"/>
-      <c r="AM51" s="4" t="inlineStr"/>
-      <c r="AN51" s="4" t="inlineStr"/>
-      <c r="AO51" s="4" t="inlineStr"/>
-      <c r="AP51" s="4" t="inlineStr"/>
-      <c r="AQ51" s="4" t="inlineStr"/>
-      <c r="AR51" s="4" t="inlineStr"/>
-      <c r="AS51" s="4" t="inlineStr"/>
-      <c r="AT51" s="4" t="inlineStr"/>
-      <c r="AU51" s="4" t="inlineStr"/>
-      <c r="AV51" s="4" t="inlineStr"/>
-      <c r="AW51" s="4" t="inlineStr">
+      <c r="AP51" s="2" t="inlineStr"/>
+      <c r="AQ51" s="2" t="inlineStr"/>
+      <c r="AR51" s="2" t="inlineStr"/>
+      <c r="AS51" s="2" t="inlineStr"/>
+      <c r="AT51" s="2" t="inlineStr"/>
+      <c r="AU51" s="2" t="inlineStr"/>
+      <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX51" s="4" t="inlineStr"/>
-      <c r="AY51" s="4" t="inlineStr"/>
-      <c r="AZ51" s="4" t="inlineStr"/>
-      <c r="BA51" s="4" t="inlineStr"/>
-      <c r="BB51" s="4" t="inlineStr">
+      <c r="AX51" s="2" t="inlineStr"/>
+      <c r="AY51" s="2" t="inlineStr"/>
+      <c r="AZ51" s="2" t="inlineStr"/>
+      <c r="BA51" s="2" t="inlineStr"/>
+      <c r="BB51" s="2" t="inlineStr">
         <is>
           <t>CMS</t>
         </is>
       </c>
-      <c r="BC51" s="4" t="inlineStr">
+      <c r="BC51" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD51" s="4" t="inlineStr"/>
-      <c r="BE51" s="4" t="inlineStr">
+      <c r="BD51" s="2" t="inlineStr"/>
+      <c r="BE51" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF51" s="4" t="inlineStr">
+      <c r="BF51" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG51" s="4" t="inlineStr">
+      <c r="BG51" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH51" s="4" t="inlineStr"/>
+      <c r="BH51" s="2" t="inlineStr"/>
+      <c r="BI51" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ51" s="2" t="inlineStr"/>
+      <c r="BK51" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9579,6 +9959,10 @@
       </c>
       <c r="BG52" s="2" t="inlineStr"/>
       <c r="BH52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BJ52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr"/>
+      <c r="BL52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9753,180 +10137,212 @@
         </is>
       </c>
       <c r="BH53" s="2" t="inlineStr"/>
+      <c r="BI53" s="2" t="inlineStr"/>
+      <c r="BJ53" s="2" t="inlineStr"/>
+      <c r="BK53" s="2" t="inlineStr"/>
+      <c r="BL53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Copart, Inc.</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T00:21:00+08:00</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Copart Rises as ACV Deal Clears Key Antitrust Hurdle</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.491</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQT3U5dFp5X3lqQjlXOExCM0FsZ2ZCUGc0dEhVMzVha1JTaGxzNzBvR1pZTUlsRVpZZjVmakcxeVU2WE5MNmN0alhGdjhsYjhiNFdkR0FFUjNGZ0k4T1ZEaHZOaXZjRnJLQXB0RndELUp0YUttSlZUSHFWbFlKZDZ6SEU4SWJyeFhjM200VDdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>隨著 ACV 交易清除關鍵的反壟斷障礙，Copart 崛起</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>47054ae9b9224d94ba76618a9113c275</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>de811dd4bd87d69099be3a3d</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>df0f258a5232fd59f2c5cad8</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+      <c r="AK54" s="2" t="inlineStr"/>
+      <c r="AL54" s="2" t="inlineStr"/>
+      <c r="AM54" s="2" t="inlineStr"/>
+      <c r="AN54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O54" s="4" t="inlineStr">
-        <is>
-          <t>0.491</t>
-        </is>
-      </c>
-      <c r="P54" s="4" t="inlineStr"/>
-      <c r="Q54" s="4" t="inlineStr"/>
-      <c r="R54" s="4" t="inlineStr"/>
-      <c r="S54" s="4" t="inlineStr"/>
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQT3U5dFp5X3lqQjlXOExCM0FsZ2ZCUGc0dEhVMzVha1JTaGxzNzBvR1pZTUlsRVpZZjVmakcxeVU2WE5MNmN0alhGdjhsYjhiNFdkR0FFUjNGZ0k4T1ZEaHZOaXZjRnJLQXB0RndELUp0YUttSlZUSHFWbFlKZDZ6SEU4SWJyeFhjM200VDdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V54" s="4" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W54" s="4" t="inlineStr">
-        <is>
-          <t>隨著 ACV 交易清除關鍵的反壟斷障礙，Copart 崛起</t>
-        </is>
-      </c>
-      <c r="X54" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y54" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA54" s="4" t="inlineStr"/>
-      <c r="AB54" s="4" t="inlineStr"/>
-      <c r="AC54" s="4" t="inlineStr">
-        <is>
-          <t>de811dd4bd87d69099be3a3d</t>
-        </is>
-      </c>
-      <c r="AD54" s="4" t="inlineStr">
-        <is>
-          <t>df0f258a5232fd59f2c5cad8</t>
-        </is>
-      </c>
-      <c r="AE54" s="4" t="inlineStr"/>
-      <c r="AF54" s="4" t="inlineStr"/>
-      <c r="AG54" s="4" t="inlineStr"/>
-      <c r="AH54" s="4" t="inlineStr"/>
-      <c r="AI54" s="4" t="inlineStr"/>
-      <c r="AJ54" s="4" t="inlineStr"/>
-      <c r="AK54" s="4" t="inlineStr"/>
-      <c r="AL54" s="4" t="inlineStr"/>
-      <c r="AM54" s="4" t="inlineStr"/>
-      <c r="AN54" s="4" t="inlineStr"/>
-      <c r="AO54" s="4" t="inlineStr"/>
-      <c r="AP54" s="4" t="inlineStr"/>
-      <c r="AQ54" s="4" t="inlineStr"/>
-      <c r="AR54" s="4" t="inlineStr"/>
-      <c r="AS54" s="4" t="inlineStr"/>
-      <c r="AT54" s="4" t="inlineStr"/>
-      <c r="AU54" s="4" t="inlineStr"/>
-      <c r="AV54" s="4" t="inlineStr"/>
-      <c r="AW54" s="4" t="inlineStr">
+      <c r="AP54" s="2" t="inlineStr"/>
+      <c r="AQ54" s="2" t="inlineStr"/>
+      <c r="AR54" s="2" t="inlineStr"/>
+      <c r="AS54" s="2" t="inlineStr"/>
+      <c r="AT54" s="2" t="inlineStr"/>
+      <c r="AU54" s="2" t="inlineStr"/>
+      <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX54" s="4" t="inlineStr"/>
-      <c r="AY54" s="4" t="inlineStr"/>
-      <c r="AZ54" s="4" t="inlineStr"/>
-      <c r="BA54" s="4" t="inlineStr"/>
-      <c r="BB54" s="4" t="inlineStr">
+      <c r="AX54" s="2" t="inlineStr"/>
+      <c r="AY54" s="2" t="inlineStr"/>
+      <c r="AZ54" s="2" t="inlineStr"/>
+      <c r="BA54" s="2" t="inlineStr"/>
+      <c r="BB54" s="2" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="BC54" s="4" t="inlineStr">
+      <c r="BC54" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD54" s="4" t="inlineStr"/>
-      <c r="BE54" s="4" t="inlineStr">
+      <c r="BD54" s="2" t="inlineStr"/>
+      <c r="BE54" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF54" s="4" t="inlineStr">
+      <c r="BF54" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG54" s="4" t="inlineStr">
+      <c r="BG54" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH54" s="4" t="inlineStr"/>
+      <c r="BH54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10093,6 +10509,10 @@
         </is>
       </c>
       <c r="BH55" s="2" t="inlineStr"/>
+      <c r="BI55" s="2" t="inlineStr"/>
+      <c r="BJ55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr"/>
+      <c r="BL55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10267,6 +10687,10 @@
         </is>
       </c>
       <c r="BH56" s="2" t="inlineStr"/>
+      <c r="BI56" s="2" t="inlineStr"/>
+      <c r="BJ56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr"/>
+      <c r="BL56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10441,6 +10865,10 @@
         </is>
       </c>
       <c r="BH57" s="2" t="inlineStr"/>
+      <c r="BI57" s="2" t="inlineStr"/>
+      <c r="BJ57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr"/>
+      <c r="BL57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -10607,6 +11035,10 @@
         </is>
       </c>
       <c r="BH58" s="3" t="inlineStr"/>
+      <c r="BI58" s="3" t="inlineStr"/>
+      <c r="BJ58" s="3" t="inlineStr"/>
+      <c r="BK58" s="3" t="inlineStr"/>
+      <c r="BL58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10781,6 +11213,10 @@
         </is>
       </c>
       <c r="BH59" s="2" t="inlineStr"/>
+      <c r="BI59" s="2" t="inlineStr"/>
+      <c r="BJ59" s="2" t="inlineStr"/>
+      <c r="BK59" s="2" t="inlineStr"/>
+      <c r="BL59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -10955,6 +11391,10 @@
         </is>
       </c>
       <c r="BH60" s="3" t="inlineStr"/>
+      <c r="BI60" s="3" t="inlineStr"/>
+      <c r="BJ60" s="3" t="inlineStr"/>
+      <c r="BK60" s="3" t="inlineStr"/>
+      <c r="BL60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11125,9 +11565,13 @@
         </is>
       </c>
       <c r="BH61" s="2" t="inlineStr"/>
+      <c r="BI61" s="2" t="inlineStr"/>
+      <c r="BJ61" s="2" t="inlineStr"/>
+      <c r="BK61" s="2" t="inlineStr"/>
+      <c r="BL61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH61"/>
+  <autoFilter ref="A1:BL61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11138,7 +11582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11201,6 +11645,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11502,6 +11950,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -11678,6 +12146,10 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11852,6 +12324,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -12026,6 +12502,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -12076,13 +12556,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -12135,7 +12619,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>664e09f00be14046869d9224b6a26606</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>9beadf3792e846e19630abb4</t>
@@ -12156,7 +12644,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -12200,6 +12692,18 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -12366,6 +12870,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -12540,524 +13048,564 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>NextEra Energy, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16T03:13:04+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NextEra Energy (NEE) Proposes Legal Settlement, Is It Still Undervalued?</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave, Inc.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T02:11:47+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave Credit Risk Hits Record, Pricing 60% Odds of Default</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>CDS利差擴大／信用風險升高</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOQ3cxbDJzTDhpNzNXR3JBZVI4OXVkLUQzcUNSUUJHam5BU1NuRUtNZUV0RXBNVlQ3bGFBV2ZoOXN3dU9HLWlockI5S1ZLZzVwMDBqTFVSTjhWcWxmeENjUUk0TGJrOUZ2OC1SNU9jRG85cnNEMDg4TmtXWHU2ZV85d3FBVUo0SG9ldmx4RjNFaEVvTnlSd1lOMndGcXhfTEwyYVJLNWZpdHpxeGNxLWVj?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>CDS_SPREAD_WIDENING</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>afa3e19288624017801f27d8504d8772</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>a997bfc9e524bb7bf0e90552</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>bb52f9b5bbfeed84bb46932d</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.119</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPVl9TTzhhQ3YyZXhfdWVNTTczZTVxbHV6V2c4cjBlQ1JfYW9oM0hJN0xrM2QxTElac0RBaDV4VEQxbFc4RERfclZwQm1xck1qdWtrNkplYWw4cU92N1V2d19zOFNsbm9DOWh1UzZEdUk5aC0yeURzTDVIVWhuem0zTVV6Y0l6V1RTRHhfeHg4YUVqR3AyLUNQUGJYQWFERWFiWnAxWE92emw0MnFzMksyVklTMUFWM3VEZlhBTkt1OUFMb05FZ0JDUDdBc9IB0AFBVV95cUxOTUp6THZvMEczYW9GZGdObEVoNnlnOFhmWDBTVmFnZnIwUU5CUERVVEFxdGY1QnVWcTVyZzdmQmFuZUhXVUhLWXVsZXpVUUFpS04yNnBpSHFCY1g1MnNyX0VEbGdKSkpDcjNTWElyY3gwVTl1MTBpNlFudEpvaktpdGg5MHhjTnF1Mi1CX1J6ckEtWUl0T3I5U0NCX21Cc2V6YnVuZkNCZFl1UG1KZGdlaDNENk5hc01ZNUJPa1pQdEtqYTVPTmJ5bC1zTTRJazZk?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t>NextEra Energy（NEE）提出法律和解，其價值是否仍被低估？</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>18cbfc1204e0da57cb84360d</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>0512a9b31af1946f9e403ace</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG8" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CoreWeave, Inc.</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T02:11:47+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>CoreWeave Credit Risk Hits Record, Pricing 60% Odds of Default</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:47:40+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Netflix layoffs: TV executives Lisa Lang McMullen, James Oh among those cut</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>'-0.89</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOQ3cxbDJzTDhpNzNXR3JBZVI4OXVkLUQzcUNSUUJHam5BU1NuRUtNZUV0RXBNVlQ3bGFBV2ZoOXN3dU9HLWlockI5S1ZLZzVwMDBqTFVSTjhWcWxmeENjUUk0TGJrOUZ2OC1SNU9jRG85cnNEMDg4TmtXWHU2ZV85d3FBVUo0SG9ldmx4RjNFaEVvTnlSd1lOMndGcXhfTEwyYVJLNWZpdHpxeGNxLWVj?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA9" s="5" t="inlineStr"/>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr">
-        <is>
-          <t>a997bfc9e524bb7bf0e90552</t>
-        </is>
-      </c>
-      <c r="AD9" s="5" t="inlineStr">
-        <is>
-          <t>bb52f9b5bbfeed84bb46932d</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr"/>
-      <c r="AF9" s="5" t="inlineStr"/>
-      <c r="AG9" s="5" t="inlineStr"/>
-      <c r="AH9" s="5" t="inlineStr"/>
-      <c r="AI9" s="5" t="inlineStr"/>
-      <c r="AJ9" s="5" t="inlineStr"/>
-      <c r="AK9" s="5" t="inlineStr"/>
-      <c r="AL9" s="5" t="inlineStr"/>
-      <c r="AM9" s="5" t="inlineStr"/>
-      <c r="AN9" s="5" t="inlineStr"/>
-      <c r="AO9" s="5" t="inlineStr"/>
-      <c r="AP9" s="5" t="inlineStr"/>
-      <c r="AQ9" s="5" t="inlineStr"/>
-      <c r="AR9" s="5" t="inlineStr"/>
-      <c r="AS9" s="5" t="inlineStr"/>
-      <c r="AT9" s="5" t="inlineStr"/>
-      <c r="AU9" s="5" t="inlineStr"/>
-      <c r="AV9" s="5" t="inlineStr"/>
-      <c r="AW9" s="5" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNNGJlRTZkeWtNdF92SEVfTnlZcWw4ZVhEck9kU1ROeTBYaWtyYlExemtubVE0dUd6bGdCNGlZdnBaZEVBMG43Q09oeTg2ekFoUTM2SHpqRWNJQ2F3RUVGTWlqTW95OWxIbEh1UVkyNy1wSkNOWk9YdXBOWmQzNVloVGRZWnloMEpqY1l2V1VGSXkyNWV4dTc0WDh4WF9wRTBqaHdPSnNHSzhoQXF0SVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>The American Bazaar</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>Netflix 裁員：電視高層 Lisa Lang McMullen、James Oh 等被裁</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>7650266cac8eba7e01b625f6</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>ec2e30886d6ecc0f3c656b08</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX9" s="5" t="inlineStr"/>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
-      <c r="BB9" s="5" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="BC9" s="5" t="inlineStr">
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="5" t="inlineStr"/>
-      <c r="BE9" s="5" t="inlineStr">
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BG9" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="5" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T01:50:13+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Starbucks/Chipotle merge rumors, True Food’s bankruptcy, and Uber’s big acquisition</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:08:00+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Netflix Layoffs: Unscripted Casting &amp; Development Execs Impacted</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>'-0.646</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.83</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQV0N6TUpTWTVrNUplM01qUVdubU9xSWNsenU3NDdoM0lkUlFOTC1Qb0xDYWRkaEY2dlkzVXJxa19KS0lJZGs3UXhkMDlzY1ZLR1NUQmdiUDVzN3NUV2NkT3BCamNZTTBXNU9fNnpERHFmTkZiZUdBeDY0NXFkYjYxQWdocGNJdkpkTXpkcWdHV3g5eTYtZVktODRFamdXTFVtck5xWTZLYl9VU0VRTllOakZMM19VYmtG?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>Nation’s Restaurant News</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr">
-        <is>
-          <t>星巴克/Chipotle 合併傳聞、True Food 破產、Uber 大舉收購</t>
-        </is>
-      </c>
-      <c r="X10" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z10" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA10" s="5" t="inlineStr"/>
-      <c r="AB10" s="5" t="inlineStr"/>
-      <c r="AC10" s="5" t="inlineStr">
-        <is>
-          <t>2548b4914d2ed2563e69c8e2</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>ce135397e6d5382cbe073479</t>
-        </is>
-      </c>
-      <c r="AE10" s="5" t="inlineStr"/>
-      <c r="AF10" s="5" t="inlineStr"/>
-      <c r="AG10" s="5" t="inlineStr"/>
-      <c r="AH10" s="5" t="inlineStr"/>
-      <c r="AI10" s="5" t="inlineStr"/>
-      <c r="AJ10" s="5" t="inlineStr"/>
-      <c r="AK10" s="5" t="inlineStr"/>
-      <c r="AL10" s="5" t="inlineStr"/>
-      <c r="AM10" s="5" t="inlineStr"/>
-      <c r="AN10" s="5" t="inlineStr"/>
-      <c r="AO10" s="5" t="inlineStr"/>
-      <c r="AP10" s="5" t="inlineStr"/>
-      <c r="AQ10" s="5" t="inlineStr"/>
-      <c r="AR10" s="5" t="inlineStr"/>
-      <c r="AS10" s="5" t="inlineStr"/>
-      <c r="AT10" s="5" t="inlineStr"/>
-      <c r="AU10" s="5" t="inlineStr"/>
-      <c r="AV10" s="5" t="inlineStr"/>
-      <c r="AW10" s="5" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="5" t="inlineStr"/>
-      <c r="AY10" s="5" t="inlineStr"/>
-      <c r="AZ10" s="5" t="inlineStr"/>
-      <c r="BA10" s="5" t="inlineStr"/>
-      <c r="BB10" s="5" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC10" s="5" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOV2lxUnNvQkFuSTlVUk43bGp1Q1MtbVpPZ24ydWNFbEdsUFZjX0ZIVWVwMDdISThReVBEUUtJNjBqV1FDV3VuV0kyUDFZaDU3YTRIY3dWOFR1QXhsYUZteHNqZ3ZJZFhpdF9TZWY2Q3dvQjZJNHFvTm9GYUFRY0xVSTl6RUk0cDNDNXU3MGNXRVA?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>Netflix 裁員：即興選角和開發高層受到影響</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>1c43b4351d14ec3d18400653</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>6bb04e409f724f1b349a51b9</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="5" t="inlineStr"/>
-      <c r="BE10" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="5" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="5" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -13072,22 +13620,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16T01:47:40+08:00</t>
+          <t>2026-10-16T01:07:33+08:00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Netflix layoffs: TV executives Lisa Lang McMullen, James Oh among those cut</t>
+          <t>PNC Financial Q3 Earnings Beat Estimates on Higher NII, Revenue Miss</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -13098,7 +13646,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>財報不如預期</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -13124,7 +13672,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>'-0.89</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr"/>
@@ -13138,44 +13686,44 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNNGJlRTZkeWtNdF92SEVfTnlZcWw4ZVhEck9kU1ROeTBYaWtyYlExemtubVE0dUd6bGdCNGlZdnBaZEVBMG43Q09oeTg2ekFoUTM2SHpqRWNJQ2F3RUVGTWlqTW95OWxIbEh1UVkyNy1wSkNOWk9YdXBOWmQzNVloVGRZWnloMEpqY1l2V1VGSXkyNWV4dTc0WDh4WF9wRTBqaHdPSnNHSzhoQXF0SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLXVGVDNMaDZqNEpBMWgzY2dQeUQwdzBfZlBLbmhWXzZZMjllRnNRVC12RUlPRFJVNnhyMmJ1NG1PemwzRnMydTJHamZpaHlLVUpFQWpfMzJWNWFVcnRHaWo4LUVDVjROYUdUNE0yTy1RdFpkS3dVWHJYNjhKQVZPak9iODA4OXBVaUlIWHBKRzJ5VmJTc3hPODJjalNmdEhZLUttejI1Q1c0SWdt?oc=5</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>The American Bazaar</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>Netflix 裁員：電視高層 Lisa Lang McMullen、James Oh 等被裁</t>
+          <t>PNC Financial 第三季獲利超出預期，因 NII 較高，營收未達預期</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>EARNINGS_MISS</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>layoff；layoffs</t>
+          <t>revenue miss</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
       <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>7650266cac8eba7e01b625f6</t>
+          <t>9505b0aa170859877a0ab133</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>ec2e30886d6ecc0f3c656b08</t>
+          <t>2587e39ff2aa09c9878f3293</t>
         </is>
       </c>
       <c r="AE11" s="3" t="inlineStr"/>
@@ -13196,18 +13744,14 @@
       <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="inlineStr"/>
       <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW11" s="3" t="inlineStr"/>
       <c r="AX11" s="3" t="inlineStr"/>
       <c r="AY11" s="3" t="inlineStr"/>
       <c r="AZ11" s="3" t="inlineStr"/>
       <c r="BA11" s="3" t="inlineStr"/>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="BC11" s="3" t="inlineStr">
@@ -13218,194 +13762,222 @@
       <c r="BD11" s="3" t="inlineStr"/>
       <c r="BE11" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF11" s="3" t="inlineStr"/>
       <c r="BG11" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T01:08:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Netflix Layoffs: Unscripted Casting &amp; Development Execs Impacted</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:01:40+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>$100M Equifax FCRA violations class action settlement</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>'-0.614</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWVlyMkJRTHp0emJNZTBFQnhlMDZMTTJJQTRJaGJVdjdma0NJQWNrdWhEUUVUYzllR3BobEoxNFpaTDJ0dG41Z01xMHBlbU4yVzhUUUlfMUpjNzVZWmtSTHZtYThMZ3YwRnNfSnpKX21NZmR2NEVYSi14em1iVlk5emxkemFKbHJWT1kzV1BJajdmLW5tRW5Ta0Q1bkRjT3BvRnJ0ZE9obFVVb1VKLU1KMF9ObVhUbzQzTU5taU01QVFtZVZr?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>Equifax FCRA 違規集體訴訟和解金額達 1 億美元</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>8db6f3649abe4d398280b8ab90bf2681</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>ada93744837e92947d202f3e</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>ec40275d5db2955cfa21f9e6</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.83</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOV2lxUnNvQkFuSTlVUk43bGp1Q1MtbVpPZ24ydWNFbEdsUFZjX0ZIVWVwMDdISThReVBEUUtJNjBqV1FDV3VuV0kyUDFZaDU3YTRIY3dWOFR1QXhsYUZteHNqZ3ZJZFhpdF9TZWY2Q3dvQjZJNHFvTm9GYUFRY0xVSTl6RUk0cDNDNXU3MGNXRVA?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t>Netflix 裁員：即興選角和開發高層受到影響</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>1c43b4351d14ec3d18400653</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>6bb04e409f724f1b349a51b9</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG12" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -13430,12 +14002,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16T01:07:33+08:00</t>
+          <t>2026-10-16T00:54:05+08:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>PNC Financial Q3 Earnings Beat Estimates on Higher NII, Revenue Miss</t>
+          <t>PNC posts strong Q3 EPS of $5.09, beating estimates despite slight revenue miss.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -13472,7 +14044,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
@@ -13486,17 +14058,17 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLXVGVDNMaDZqNEpBMWgzY2dQeUQwdzBfZlBLbmhWXzZZMjllRnNRVC12RUlPRFJVNnhyMmJ1NG1PemwzRnMydTJHamZpaHlLVUpFQWpfMzJWNWFVcnRHaWo4LUVDVjROYUdUNE0yTy1RdFpkS3dVWHJYNjhKQVZPak9iODA4OXBVaUlIWHBKRzJ5VmJTc3hPODJjalNmdEhZLUttejI1Q1c0SWdt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeFhEN2xkdjgyb0U1cjcwZ3NBVkRwaG5EQzU4aEFBdFlwV0FrbXdESHpBVXpvbmdad1BObDItekdKX2ppeVp1bG93WE81MVhDemdzcy1IX2pwNlptcWVabVZOSENNaDV4bFR4LWtlaDM4Q0tXWVptZ0JZYlJxNkxDXzR6aFFpem9R?oc=5</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>PNC Financial 第三季獲利超出預期，因 NII 較高，營收未達預期</t>
+          <t>PNC 第三季每股收益強勁，達到 5.09 美元，儘管收入略有下降，但仍超出預期。</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -13518,12 +14090,12 @@
       <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>9505b0aa170859877a0ab133</t>
+          <t>6a2633ad31b6c50e33125bed</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>2587e39ff2aa09c9878f3293</t>
+          <t>d7a7e70cfcdca5486b0593a1</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr"/>
@@ -13572,180 +14144,208 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16T01:01:40+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>$100M Equifax FCRA violations class action settlement</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave, Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:52:16+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave credit default swaps hit distress levels as investors sour on AI debt</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>CDS利差擴大／信用風險升高</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>CDS_SPREAD_WIDENING</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>9a2cf57383d049b595007302e6da1711</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>15701a5080a3de1ba6257ef1</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>0040b1fc371664e2cde9c86e</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.614</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWVlyMkJRTHp0emJNZTBFQnhlMDZMTTJJQTRJaGJVdjdma0NJQWNrdWhEUUVUYzllR3BobEoxNFpaTDJ0dG41Z01xMHBlbU4yVzhUUUlfMUpjNzVZWmtSTHZtYThMZ3YwRnNfSnpKX21NZmR2NEVYSi14em1iVlk5emxkemFKbHJWT1kzV1BJajdmLW5tRW5Ta0Q1bkRjT3BvRnJ0ZE9obFVVb1VKLU1KMF9ObVhUbzQzTU5taU01QVFtZVZr?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>Equifax FCRA 違規集體訴訟和解金額達 1 億美元</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>ada93744837e92947d202f3e</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>ec40275d5db2955cfa21f9e6</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr"/>
+      <c r="AY14" s="3" t="inlineStr"/>
+      <c r="AZ14" s="3" t="inlineStr"/>
+      <c r="BA14" s="3" t="inlineStr"/>
+      <c r="BB14" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="BC14" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="4" t="inlineStr">
+      <c r="BD14" s="3" t="inlineStr"/>
+      <c r="BE14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG14" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -13760,22 +14360,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16T00:54:05+08:00</t>
+          <t>2026-10-16T00:13:28+08:00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>PNC posts strong Q3 EPS of $5.09, beating estimates despite slight revenue miss.</t>
+          <t>Fastenal Flashes Bullish Signal as Uptrend Holds Despite Margin Pressure</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -13786,7 +14386,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>營運惡化</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -13812,7 +14412,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>0.908</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr"/>
@@ -13826,44 +14426,44 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeFhEN2xkdjgyb0U1cjcwZ3NBVkRwaG5EQzU4aEFBdFlwV0FrbXdESHpBVXpvbmdad1BObDItekdKX2ppeVp1bG93WE81MVhDemdzcy1IX2pwNlptcWVabVZOSENNaDV4bFR4LWtlaDM4Q0tXWVptZ0JZYlJxNkxDXzR6aFFpem9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWDFrVktXTms4Yk9Edk5VaDlIQ3pQVENZb29UclljTnlubExOTWFNV1ZOVEQwUEVqOEVRQUxuVGVfcTRmaU9CRTdOd2tweGhSR1E0N0xnNHlpZy1XelVSRU00cTNsNXRRRnZOR1lwVk9JMEkwSk95YlFZVlh4Q2NqSEp6blhoR1ZGclZ5MkFnam0tbjhwY2tVSzJzbUtfWUd2NVJpcmlXcmtIWDhsamc?oc=5</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>PNC 第三季每股收益強勁，達到 5.09 美元，儘管收入略有下降，但仍超出預期。</t>
+          <t>儘管利潤率面臨壓力，但仍保持上升趨勢，Fastenal 閃爍看漲訊號</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>OPERATING_DETERIORATION</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>revenue miss</t>
+          <t>margin pressure</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
       <c r="AB15" s="3" t="inlineStr"/>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>6a2633ad31b6c50e33125bed</t>
+          <t>f5e0ef07093c7b595505d4a8</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>d7a7e70cfcdca5486b0593a1</t>
+          <t>6decca22cb7377dd62f5f73e</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr"/>
@@ -13891,7 +14491,7 @@
       <c r="BA15" s="3" t="inlineStr"/>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="BC15" s="3" t="inlineStr">
@@ -13912,867 +14512,191 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CoreWeave, Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:52:16+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>CoreWeave credit default swaps hit distress levels as investors sour on AI debt</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Zoetis Inc. Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:04:05+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Zoetis (ZTS) Hit by Guidance Cuts, Met with Market Shrug</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>財測下修</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>'-0.461</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
-      <c r="X16" s="5" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnVrVExqQ0pNWmhOR2U1VkZMVFpVMFFrZV9tVFloa1Bub3NnQnRSRGc2ME5icmt5SXNxNXRhT2VjRE5JdGlkLWxsRWNLbWV1SENjYUYzNEN2UE5GSnhqQXV4aXNINVdFV2Vyb3RrYTlCZks2MFhmU0U4Z01xaVhQeGM1bGN6QW5PVm9neXNJclFaUlE?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>Zoetis (ZTS) 受到指導性下調的打擊，市場對此不以為然</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA16" s="5" t="inlineStr"/>
-      <c r="AB16" s="5" t="inlineStr"/>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>15701a5080a3de1ba6257ef1</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>0040b1fc371664e2cde9c86e</t>
-        </is>
-      </c>
-      <c r="AE16" s="5" t="inlineStr"/>
-      <c r="AF16" s="5" t="inlineStr"/>
-      <c r="AG16" s="5" t="inlineStr"/>
-      <c r="AH16" s="5" t="inlineStr"/>
-      <c r="AI16" s="5" t="inlineStr"/>
-      <c r="AJ16" s="5" t="inlineStr"/>
-      <c r="AK16" s="5" t="inlineStr"/>
-      <c r="AL16" s="5" t="inlineStr"/>
-      <c r="AM16" s="5" t="inlineStr"/>
-      <c r="AN16" s="5" t="inlineStr"/>
-      <c r="AO16" s="5" t="inlineStr"/>
-      <c r="AP16" s="5" t="inlineStr"/>
-      <c r="AQ16" s="5" t="inlineStr"/>
-      <c r="AR16" s="5" t="inlineStr"/>
-      <c r="AS16" s="5" t="inlineStr"/>
-      <c r="AT16" s="5" t="inlineStr"/>
-      <c r="AU16" s="5" t="inlineStr"/>
-      <c r="AV16" s="5" t="inlineStr"/>
-      <c r="AW16" s="5" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX16" s="5" t="inlineStr"/>
-      <c r="AY16" s="5" t="inlineStr"/>
-      <c r="AZ16" s="5" t="inlineStr"/>
-      <c r="BA16" s="5" t="inlineStr"/>
-      <c r="BB16" s="5" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="BC16" s="5" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>EARNINGS_WARNING</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>guidance cut</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>9f004fe961a36687ee0eb7c3</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>7512ff6d3ceb5edadd9ce246</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="5" t="inlineStr"/>
-      <c r="BE16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="5" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>CMS</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>CMS Energy Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:30:25+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>FTC to Healthcare Providers: CMS Price Transparency Compliance Is Not Safe Harbor</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>'-0.583</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbS1rWDVwMExxOHVRaU5Gbk11NmVZT3FzcnFoMFJ3MDQzSmVYLS1UZnlTV3A1bVBpQXltTldjNV9Wd2xoUC0wWkhYdTVwMU9Za3N3V3U4X0FYb3g3WHFCMjRvUVg4RXBFS1ZLZXJUM3FYZThPUXQ3bmdLbGZNZ0M4WWRMRVJqZUpQd2o5LVJvSVlSZFhuMVJ4WDkzYnhiM0VEbVVPS0RFM1lrZjZmQ2FWd0hXeVd5R0pyVzRfNlpUMUxMQTh4NkNLUDR2ZDdXRjloTkFQZmNGTzBSQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>McGuireWoods</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>FTC 致醫療保健提供者：CMS 價格透明度合規並非安全港</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>b57f1ae761039b095c1a3b9f</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>bacf34c1ecdf56c4b714001b</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="4" t="inlineStr"/>
-      <c r="AZ17" s="4" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t>CMS</t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Copart, Inc.</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:21:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Copart Rises as ACV Deal Clears Key Antitrust Hurdle</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.491</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQT3U5dFp5X3lqQjlXOExCM0FsZ2ZCUGc0dEhVMzVha1JTaGxzNzBvR1pZTUlsRVpZZjVmakcxeVU2WE5MNmN0alhGdjhsYjhiNFdkR0FFUjNGZ0k4T1ZEaHZOaXZjRnJLQXB0RndELUp0YUttSlZUSHFWbFlKZDZ6SEU4SWJyeFhjM200VDdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>隨著 ACV 交易清除關鍵的反壟斷障礙，Copart 崛起</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>de811dd4bd87d69099be3a3d</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>df0f258a5232fd59f2c5cad8</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:13:28+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Fastenal Flashes Bullish Signal as Uptrend Holds Despite Margin Pressure</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWDFrVktXTms4Yk9Edk5VaDlIQ3pQVENZb29UclljTnlubExOTWFNV1ZOVEQwUEVqOEVRQUxuVGVfcTRmaU9CRTdOd2tweGhSR1E0N0xnNHlpZy1XelVSRU00cTNsNXRRRnZOR1lwVk9JMEkwSk95YlFZVlh4Q2NqSEp6blhoR1ZGclZ5MkFnam0tbjhwY2tVSzJzbUtfWUd2NVJpcmlXcmtIWDhsamc?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t>儘管利潤率面臨壓力，但仍保持上升趨勢，Fastenal 閃爍看漲訊號</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr">
-        <is>
-          <t>f5e0ef07093c7b595505d4a8</t>
-        </is>
-      </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>6decca22cb7377dd62f5f73e</t>
-        </is>
-      </c>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr"/>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC19" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF19" s="3" t="inlineStr"/>
-      <c r="BG19" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>ZTS</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:04:05+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis (ZTS) Hit by Guidance Cuts, Met with Market Shrug</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>'-0.461</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnVrVExqQ0pNWmhOR2U1VkZMVFpVMFFrZV9tVFloa1Bub3NnQnRSRGc2ME5icmt5SXNxNXRhT2VjRE5JdGlkLWxsRWNLbWV1SENjYUYzNEN2UE5GSnhqQXV4aXNINVdFV2Vyb3RrYTlCZks2MFhmU0U4Z01xaVhQeGM1bGN6QW5PVm9neXNJclFaUlE?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis (ZTS) 受到指導性下調的打擊，市場對此不以為然</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>guidance cut</t>
-        </is>
-      </c>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr">
-        <is>
-          <t>9f004fe961a36687ee0eb7c3</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>7512ff6d3ceb5edadd9ce246</t>
-        </is>
-      </c>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
-      <c r="AM20" s="3" t="inlineStr"/>
-      <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
-      <c r="AV20" s="3" t="inlineStr"/>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr"/>
-      <c r="AY20" s="3" t="inlineStr"/>
-      <c r="AZ20" s="3" t="inlineStr"/>
-      <c r="BA20" s="3" t="inlineStr"/>
-      <c r="BB20" s="3" t="inlineStr">
-        <is>
-          <t>ZTS</t>
-        </is>
-      </c>
-      <c r="BC20" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="3" t="inlineStr"/>
-      <c r="BE20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG20" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH20"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14783,7 +14707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14846,6 +14770,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15147,6 +15075,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -15323,9 +15271,13 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15336,7 +15288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15399,6 +15351,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15702,9 +15658,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15715,7 +15691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15765,134 +15741,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -15902,46 +15878,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -15950,12 +15960,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -15965,90 +15975,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -16058,94 +16072,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -16153,89 +16167,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-16.xlsx
+++ b/news_daily/2026-10-16.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -3177,13 +3177,17 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3236,7 +3240,11 @@
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>2c9b939b25da42639699f228fb1494d7</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>e140caa4ed6aafbe859ecd7f</t>
@@ -3257,7 +3265,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -3303,8 +3315,16 @@
       <c r="BH15" s="3" t="inlineStr"/>
       <c r="BI15" s="3" t="inlineStr"/>
       <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4407,13 +4427,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4466,7 +4490,11 @@
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>3ab496c675864a1cb9bc5e83ad25de4d</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>63de804502bebab350895bcf</t>
@@ -4487,7 +4515,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4533,8 +4565,16 @@
       <c r="BH22" s="3" t="inlineStr"/>
       <c r="BI22" s="3" t="inlineStr"/>
       <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4585,13 +4625,17 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -4644,7 +4688,11 @@
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>fb43d140a4114416ae2d6cef5f8e4d61</t>
+        </is>
+      </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
           <t>142a0a66ae71a6cf66297fa4</t>
@@ -4665,7 +4713,11 @@
       <c r="AL23" s="3" t="inlineStr"/>
       <c r="AM23" s="3" t="inlineStr"/>
       <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="3" t="inlineStr"/>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
@@ -4711,8 +4763,16 @@
       <c r="BH23" s="3" t="inlineStr"/>
       <c r="BI23" s="3" t="inlineStr"/>
       <c r="BJ23" s="3" t="inlineStr"/>
-      <c r="BK23" s="3" t="inlineStr"/>
-      <c r="BL23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -6179,13 +6239,17 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -6238,7 +6302,11 @@
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr"/>
-      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>8a31e358ff064b3e8edce3793df2b3eb</t>
+        </is>
+      </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>4b6843ea2864f85d882e5987</t>
@@ -6259,7 +6327,11 @@
       <c r="AL32" s="3" t="inlineStr"/>
       <c r="AM32" s="3" t="inlineStr"/>
       <c r="AN32" s="3" t="inlineStr"/>
-      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="3" t="inlineStr"/>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr"/>
@@ -6297,8 +6369,16 @@
       <c r="BH32" s="3" t="inlineStr"/>
       <c r="BI32" s="3" t="inlineStr"/>
       <c r="BJ32" s="3" t="inlineStr"/>
-      <c r="BK32" s="3" t="inlineStr"/>
-      <c r="BL32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6867,13 +6947,17 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -6926,7 +7010,11 @@
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr"/>
-      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>3ac489b3085048599c2ffa08158088b2</t>
+        </is>
+      </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
           <t>6a1dec628ebbf7eaf702f172</t>
@@ -6947,7 +7035,11 @@
       <c r="AL36" s="3" t="inlineStr"/>
       <c r="AM36" s="3" t="inlineStr"/>
       <c r="AN36" s="3" t="inlineStr"/>
-      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="3" t="inlineStr"/>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr"/>
@@ -6993,8 +7085,16 @@
       <c r="BH36" s="3" t="inlineStr"/>
       <c r="BI36" s="3" t="inlineStr"/>
       <c r="BJ36" s="3" t="inlineStr"/>
-      <c r="BK36" s="3" t="inlineStr"/>
-      <c r="BL36" s="3" t="inlineStr"/>
+      <c r="BK36" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -8181,13 +8281,17 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -8240,7 +8344,11 @@
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr"/>
-      <c r="AB43" s="3" t="inlineStr"/>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>979c6de56e88420d8ca1a04da3a5cdd8</t>
+        </is>
+      </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
           <t>7650266cac8eba7e01b625f6</t>
@@ -8261,7 +8369,11 @@
       <c r="AL43" s="3" t="inlineStr"/>
       <c r="AM43" s="3" t="inlineStr"/>
       <c r="AN43" s="3" t="inlineStr"/>
-      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP43" s="3" t="inlineStr"/>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr"/>
@@ -8307,8 +8419,16 @@
       <c r="BH43" s="3" t="inlineStr"/>
       <c r="BI43" s="3" t="inlineStr"/>
       <c r="BJ43" s="3" t="inlineStr"/>
-      <c r="BK43" s="3" t="inlineStr"/>
-      <c r="BL43" s="3" t="inlineStr"/>
+      <c r="BK43" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -8359,13 +8479,17 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -8418,7 +8542,11 @@
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr"/>
-      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>64c8938b9f384dfc8de6f04fe35535b2</t>
+        </is>
+      </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
           <t>1c43b4351d14ec3d18400653</t>
@@ -8439,7 +8567,11 @@
       <c r="AL44" s="3" t="inlineStr"/>
       <c r="AM44" s="3" t="inlineStr"/>
       <c r="AN44" s="3" t="inlineStr"/>
-      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP44" s="3" t="inlineStr"/>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr"/>
@@ -8485,178 +8617,210 @@
       <c r="BH44" s="3" t="inlineStr"/>
       <c r="BI44" s="3" t="inlineStr"/>
       <c r="BJ44" s="3" t="inlineStr"/>
-      <c r="BK44" s="3" t="inlineStr"/>
-      <c r="BL44" s="3" t="inlineStr"/>
+      <c r="BK44" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>PNC</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>PNC Financial Services</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T01:07:33+08:00</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>PNC Financial Q3 Earnings Beat Estimates on Higher NII, Revenue Miss</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLXVGVDNMaDZqNEpBMWgzY2dQeUQwdzBfZlBLbmhWXzZZMjllRnNRVC12RUlPRFJVNnhyMmJ1NG1PemwzRnMydTJHamZpaHlLVUpFQWpfMzJWNWFVcnRHaWo4LUVDVjROYUdUNE0yTy1RdFpkS3dVWHJYNjhKQVZPak9iODA4OXBVaUlIWHBKRzJ5VmJTc3hPODJjalNmdEhZLUttejI1Q1c0SWdt?oc=5</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Zacks Investment Research</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>PNC Financial 第三季獲利超出預期，因 NII 較高，營收未達預期</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>revenue miss</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>bae707365bb64f55aedf616b3f0d6668</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9505b0aa170859877a0ab133</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>2587e39ff2aa09c9878f3293</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="inlineStr"/>
+      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AM45" s="2" t="inlineStr"/>
+      <c r="AN45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLXVGVDNMaDZqNEpBMWgzY2dQeUQwdzBfZlBLbmhWXzZZMjllRnNRVC12RUlPRFJVNnhyMmJ1NG1PemwzRnMydTJHamZpaHlLVUpFQWpfMzJWNWFVcnRHaWo4LUVDVjROYUdUNE0yTy1RdFpkS3dVWHJYNjhKQVZPak9iODA4OXBVaUlIWHBKRzJ5VmJTc3hPODJjalNmdEhZLUttejI1Q1c0SWdt?oc=5</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>Zacks Investment Research</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>PNC Financial 第三季獲利超出預期，因 NII 較高，營收未達預期</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>revenue miss</t>
-        </is>
-      </c>
-      <c r="AA45" s="3" t="inlineStr"/>
-      <c r="AB45" s="3" t="inlineStr"/>
-      <c r="AC45" s="3" t="inlineStr">
-        <is>
-          <t>9505b0aa170859877a0ab133</t>
-        </is>
-      </c>
-      <c r="AD45" s="3" t="inlineStr">
-        <is>
-          <t>2587e39ff2aa09c9878f3293</t>
-        </is>
-      </c>
-      <c r="AE45" s="3" t="inlineStr"/>
-      <c r="AF45" s="3" t="inlineStr"/>
-      <c r="AG45" s="3" t="inlineStr"/>
-      <c r="AH45" s="3" t="inlineStr"/>
-      <c r="AI45" s="3" t="inlineStr"/>
-      <c r="AJ45" s="3" t="inlineStr"/>
-      <c r="AK45" s="3" t="inlineStr"/>
-      <c r="AL45" s="3" t="inlineStr"/>
-      <c r="AM45" s="3" t="inlineStr"/>
-      <c r="AN45" s="3" t="inlineStr"/>
-      <c r="AO45" s="3" t="inlineStr"/>
-      <c r="AP45" s="3" t="inlineStr"/>
-      <c r="AQ45" s="3" t="inlineStr"/>
-      <c r="AR45" s="3" t="inlineStr"/>
-      <c r="AS45" s="3" t="inlineStr"/>
-      <c r="AT45" s="3" t="inlineStr"/>
-      <c r="AU45" s="3" t="inlineStr"/>
-      <c r="AV45" s="3" t="inlineStr"/>
-      <c r="AW45" s="3" t="inlineStr"/>
-      <c r="AX45" s="3" t="inlineStr"/>
-      <c r="AY45" s="3" t="inlineStr"/>
-      <c r="AZ45" s="3" t="inlineStr"/>
-      <c r="BA45" s="3" t="inlineStr"/>
-      <c r="BB45" s="3" t="inlineStr">
+      <c r="AP45" s="2" t="inlineStr"/>
+      <c r="AQ45" s="2" t="inlineStr"/>
+      <c r="AR45" s="2" t="inlineStr"/>
+      <c r="AS45" s="2" t="inlineStr"/>
+      <c r="AT45" s="2" t="inlineStr"/>
+      <c r="AU45" s="2" t="inlineStr"/>
+      <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" s="2" t="inlineStr"/>
+      <c r="AX45" s="2" t="inlineStr"/>
+      <c r="AY45" s="2" t="inlineStr"/>
+      <c r="AZ45" s="2" t="inlineStr"/>
+      <c r="BA45" s="2" t="inlineStr"/>
+      <c r="BB45" s="2" t="inlineStr">
         <is>
           <t>PNC</t>
         </is>
       </c>
-      <c r="BC45" s="3" t="inlineStr">
+      <c r="BC45" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD45" s="3" t="inlineStr"/>
-      <c r="BE45" s="3" t="inlineStr">
+      <c r="BD45" s="2" t="inlineStr"/>
+      <c r="BE45" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF45" s="3" t="inlineStr"/>
-      <c r="BG45" s="3" t="inlineStr">
+      <c r="BF45" s="2" t="inlineStr"/>
+      <c r="BG45" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH45" s="3" t="inlineStr"/>
-      <c r="BI45" s="3" t="inlineStr"/>
-      <c r="BJ45" s="3" t="inlineStr"/>
-      <c r="BK45" s="3" t="inlineStr"/>
-      <c r="BL45" s="3" t="inlineStr"/>
+      <c r="BH45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -9039,174 +9203,198 @@
       <c r="BL47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>PNC</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>PNC Financial Services</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T00:54:05+08:00</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>PNC posts strong Q3 EPS of $5.09, beating estimates despite slight revenue miss.</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.915</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeFhEN2xkdjgyb0U1cjcwZ3NBVkRwaG5EQzU4aEFBdFlwV0FrbXdESHpBVXpvbmdad1BObDItekdKX2ppeVp1bG93WE81MVhDemdzcy1IX2pwNlptcWVabVZOSENNaDV4bFR4LWtlaDM4Q0tXWVptZ0JZYlJxNkxDXzR6aFFpem9R?oc=5</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Pluang</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>PNC 第三季每股收益強勁，達到 5.09 美元，儘管收入略有下降，但仍超出預期。</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>revenue miss</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>a13de172d2d94774ac8ebf195293e56b</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6a2633ad31b6c50e33125bed</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>d7a7e70cfcdca5486b0593a1</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+      <c r="AK48" s="2" t="inlineStr"/>
+      <c r="AL48" s="2" t="inlineStr"/>
+      <c r="AM48" s="2" t="inlineStr"/>
+      <c r="AN48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr"/>
-      <c r="R48" s="3" t="inlineStr"/>
-      <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U48" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeFhEN2xkdjgyb0U1cjcwZ3NBVkRwaG5EQzU4aEFBdFlwV0FrbXdESHpBVXpvbmdad1BObDItekdKX2ppeVp1bG93WE81MVhDemdzcy1IX2pwNlptcWVabVZOSENNaDV4bFR4LWtlaDM4Q0tXWVptZ0JZYlJxNkxDXzR6aFFpem9R?oc=5</t>
-        </is>
-      </c>
-      <c r="V48" s="3" t="inlineStr">
-        <is>
-          <t>Pluang</t>
-        </is>
-      </c>
-      <c r="W48" s="3" t="inlineStr">
-        <is>
-          <t>PNC 第三季每股收益強勁，達到 5.09 美元，儘管收入略有下降，但仍超出預期。</t>
-        </is>
-      </c>
-      <c r="X48" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>revenue miss</t>
-        </is>
-      </c>
-      <c r="AA48" s="3" t="inlineStr"/>
-      <c r="AB48" s="3" t="inlineStr"/>
-      <c r="AC48" s="3" t="inlineStr">
-        <is>
-          <t>6a2633ad31b6c50e33125bed</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>d7a7e70cfcdca5486b0593a1</t>
-        </is>
-      </c>
-      <c r="AE48" s="3" t="inlineStr"/>
-      <c r="AF48" s="3" t="inlineStr"/>
-      <c r="AG48" s="3" t="inlineStr"/>
-      <c r="AH48" s="3" t="inlineStr"/>
-      <c r="AI48" s="3" t="inlineStr"/>
-      <c r="AJ48" s="3" t="inlineStr"/>
-      <c r="AK48" s="3" t="inlineStr"/>
-      <c r="AL48" s="3" t="inlineStr"/>
-      <c r="AM48" s="3" t="inlineStr"/>
-      <c r="AN48" s="3" t="inlineStr"/>
-      <c r="AO48" s="3" t="inlineStr"/>
-      <c r="AP48" s="3" t="inlineStr"/>
-      <c r="AQ48" s="3" t="inlineStr"/>
-      <c r="AR48" s="3" t="inlineStr"/>
-      <c r="AS48" s="3" t="inlineStr"/>
-      <c r="AT48" s="3" t="inlineStr"/>
-      <c r="AU48" s="3" t="inlineStr"/>
-      <c r="AV48" s="3" t="inlineStr"/>
-      <c r="AW48" s="3" t="inlineStr"/>
-      <c r="AX48" s="3" t="inlineStr"/>
-      <c r="AY48" s="3" t="inlineStr"/>
-      <c r="AZ48" s="3" t="inlineStr"/>
-      <c r="BA48" s="3" t="inlineStr"/>
-      <c r="BB48" s="3" t="inlineStr">
+      <c r="AP48" s="2" t="inlineStr"/>
+      <c r="AQ48" s="2" t="inlineStr"/>
+      <c r="AR48" s="2" t="inlineStr"/>
+      <c r="AS48" s="2" t="inlineStr"/>
+      <c r="AT48" s="2" t="inlineStr"/>
+      <c r="AU48" s="2" t="inlineStr"/>
+      <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" s="2" t="inlineStr"/>
+      <c r="AX48" s="2" t="inlineStr"/>
+      <c r="AY48" s="2" t="inlineStr"/>
+      <c r="AZ48" s="2" t="inlineStr"/>
+      <c r="BA48" s="2" t="inlineStr"/>
+      <c r="BB48" s="2" t="inlineStr">
         <is>
           <t>PNC</t>
         </is>
       </c>
-      <c r="BC48" s="3" t="inlineStr">
+      <c r="BC48" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD48" s="3" t="inlineStr"/>
-      <c r="BE48" s="3" t="inlineStr">
+      <c r="BD48" s="2" t="inlineStr"/>
+      <c r="BE48" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF48" s="3" t="inlineStr"/>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BF48" s="2" t="inlineStr"/>
+      <c r="BG48" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH48" s="3" t="inlineStr"/>
-      <c r="BI48" s="3" t="inlineStr"/>
-      <c r="BJ48" s="3" t="inlineStr"/>
-      <c r="BK48" s="3" t="inlineStr"/>
-      <c r="BL48" s="3" t="inlineStr"/>
+      <c r="BH48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -9816,32 +10004,32 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -9885,7 +10073,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -9894,7 +10082,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>9186ef545b6149a2bfb894e98fc2a75f</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>772d4856366ece14d22e6307</t>
@@ -9917,7 +10109,7 @@
       <c r="AN52" s="2" t="inlineStr"/>
       <c r="AO52" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP52" s="2" t="inlineStr"/>
@@ -9959,10 +10151,22 @@
       </c>
       <c r="BG52" s="2" t="inlineStr"/>
       <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10871,174 +11075,198 @@
       <c r="BL57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fastenal</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>2026-10-16T00:13:28+08:00</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Fastenal Flashes Bullish Signal as Uptrend Holds Despite Margin Pressure</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.908</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWDFrVktXTms4Yk9Edk5VaDlIQ3pQVENZb29UclljTnlubExOTWFNV1ZOVEQwUEVqOEVRQUxuVGVfcTRmaU9CRTdOd2tweGhSR1E0N0xnNHlpZy1XelVSRU00cTNsNXRRRnZOR1lwVk9JMEkwSk95YlFZVlh4Q2NqSEp6blhoR1ZGclZ5MkFnam0tbjhwY2tVSzJzbUtfWUd2NVJpcmlXcmtIWDhsamc?oc=5</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>儘管利潤率面臨壓力，但仍保持上升趨勢，Fastenal 閃爍看漲訊號</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>594ada4f6d5741869c416c42b9f195e3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>f5e0ef07093c7b595505d4a8</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>6decca22cb7377dd62f5f73e</t>
+        </is>
+      </c>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+      <c r="AK58" s="2" t="inlineStr"/>
+      <c r="AL58" s="2" t="inlineStr"/>
+      <c r="AM58" s="2" t="inlineStr"/>
+      <c r="AN58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="3" t="inlineStr"/>
-      <c r="R58" s="3" t="inlineStr"/>
-      <c r="S58" s="3" t="inlineStr"/>
-      <c r="T58" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U58" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWDFrVktXTms4Yk9Edk5VaDlIQ3pQVENZb29UclljTnlubExOTWFNV1ZOVEQwUEVqOEVRQUxuVGVfcTRmaU9CRTdOd2tweGhSR1E0N0xnNHlpZy1XelVSRU00cTNsNXRRRnZOR1lwVk9JMEkwSk95YlFZVlh4Q2NqSEp6blhoR1ZGclZ5MkFnam0tbjhwY2tVSzJzbUtfWUd2NVJpcmlXcmtIWDhsamc?oc=5</t>
-        </is>
-      </c>
-      <c r="V58" s="3" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="W58" s="3" t="inlineStr">
-        <is>
-          <t>儘管利潤率面臨壓力，但仍保持上升趨勢，Fastenal 閃爍看漲訊號</t>
-        </is>
-      </c>
-      <c r="X58" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z58" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA58" s="3" t="inlineStr"/>
-      <c r="AB58" s="3" t="inlineStr"/>
-      <c r="AC58" s="3" t="inlineStr">
-        <is>
-          <t>f5e0ef07093c7b595505d4a8</t>
-        </is>
-      </c>
-      <c r="AD58" s="3" t="inlineStr">
-        <is>
-          <t>6decca22cb7377dd62f5f73e</t>
-        </is>
-      </c>
-      <c r="AE58" s="3" t="inlineStr"/>
-      <c r="AF58" s="3" t="inlineStr"/>
-      <c r="AG58" s="3" t="inlineStr"/>
-      <c r="AH58" s="3" t="inlineStr"/>
-      <c r="AI58" s="3" t="inlineStr"/>
-      <c r="AJ58" s="3" t="inlineStr"/>
-      <c r="AK58" s="3" t="inlineStr"/>
-      <c r="AL58" s="3" t="inlineStr"/>
-      <c r="AM58" s="3" t="inlineStr"/>
-      <c r="AN58" s="3" t="inlineStr"/>
-      <c r="AO58" s="3" t="inlineStr"/>
-      <c r="AP58" s="3" t="inlineStr"/>
-      <c r="AQ58" s="3" t="inlineStr"/>
-      <c r="AR58" s="3" t="inlineStr"/>
-      <c r="AS58" s="3" t="inlineStr"/>
-      <c r="AT58" s="3" t="inlineStr"/>
-      <c r="AU58" s="3" t="inlineStr"/>
-      <c r="AV58" s="3" t="inlineStr"/>
-      <c r="AW58" s="3" t="inlineStr"/>
-      <c r="AX58" s="3" t="inlineStr"/>
-      <c r="AY58" s="3" t="inlineStr"/>
-      <c r="AZ58" s="3" t="inlineStr"/>
-      <c r="BA58" s="3" t="inlineStr"/>
-      <c r="BB58" s="3" t="inlineStr">
+      <c r="AP58" s="2" t="inlineStr"/>
+      <c r="AQ58" s="2" t="inlineStr"/>
+      <c r="AR58" s="2" t="inlineStr"/>
+      <c r="AS58" s="2" t="inlineStr"/>
+      <c r="AT58" s="2" t="inlineStr"/>
+      <c r="AU58" s="2" t="inlineStr"/>
+      <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" s="2" t="inlineStr"/>
+      <c r="AX58" s="2" t="inlineStr"/>
+      <c r="AY58" s="2" t="inlineStr"/>
+      <c r="AZ58" s="2" t="inlineStr"/>
+      <c r="BA58" s="2" t="inlineStr"/>
+      <c r="BB58" s="2" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
-      <c r="BC58" s="3" t="inlineStr">
+      <c r="BC58" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD58" s="3" t="inlineStr"/>
-      <c r="BE58" s="3" t="inlineStr">
+      <c r="BD58" s="2" t="inlineStr"/>
+      <c r="BE58" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF58" s="3" t="inlineStr"/>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BF58" s="2" t="inlineStr"/>
+      <c r="BG58" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH58" s="3" t="inlineStr"/>
-      <c r="BI58" s="3" t="inlineStr"/>
-      <c r="BJ58" s="3" t="inlineStr"/>
-      <c r="BK58" s="3" t="inlineStr"/>
-      <c r="BL58" s="3" t="inlineStr"/>
+      <c r="BH58" s="2" t="inlineStr"/>
+      <c r="BI58" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ58" s="2" t="inlineStr"/>
+      <c r="BK58" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11267,13 +11495,17 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -11326,7 +11558,11 @@
         </is>
       </c>
       <c r="AA60" s="3" t="inlineStr"/>
-      <c r="AB60" s="3" t="inlineStr"/>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>f7f3806f53354a81a6835571d4ca8e53</t>
+        </is>
+      </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
           <t>9f004fe961a36687ee0eb7c3</t>
@@ -11347,7 +11583,11 @@
       <c r="AL60" s="3" t="inlineStr"/>
       <c r="AM60" s="3" t="inlineStr"/>
       <c r="AN60" s="3" t="inlineStr"/>
-      <c r="AO60" s="3" t="inlineStr"/>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP60" s="3" t="inlineStr"/>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr"/>
@@ -11393,8 +11633,16 @@
       <c r="BH60" s="3" t="inlineStr"/>
       <c r="BI60" s="3" t="inlineStr"/>
       <c r="BJ60" s="3" t="inlineStr"/>
-      <c r="BK60" s="3" t="inlineStr"/>
-      <c r="BL60" s="3" t="inlineStr"/>
+      <c r="BK60" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11582,7 +11830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL16"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12022,13 +12270,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -12081,7 +12333,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>2c9b939b25da42639699f228fb1494d7</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>e140caa4ed6aafbe859ecd7f</t>
@@ -12102,7 +12358,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -12148,8 +12408,16 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -12200,13 +12468,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -12259,7 +12531,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>3ab496c675864a1cb9bc5e83ad25de4d</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>63de804502bebab350895bcf</t>
@@ -12280,7 +12556,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -12326,8 +12606,16 @@
       <c r="BH3" s="3" t="inlineStr"/>
       <c r="BI3" s="3" t="inlineStr"/>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -12378,13 +12666,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -12437,7 +12729,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>fb43d140a4114416ae2d6cef5f8e4d61</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>142a0a66ae71a6cf66297fa4</t>
@@ -12458,7 +12754,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -12504,8 +12804,16 @@
       <c r="BH4" s="3" t="inlineStr"/>
       <c r="BI4" s="3" t="inlineStr"/>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -12754,13 +13062,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -12813,7 +13125,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>8a31e358ff064b3e8edce3793df2b3eb</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>4b6843ea2864f85d882e5987</t>
@@ -12834,7 +13150,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -12872,8 +13192,16 @@
       <c r="BH6" s="3" t="inlineStr"/>
       <c r="BI6" s="3" t="inlineStr"/>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -12924,13 +13252,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -12983,7 +13315,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>3ac489b3085048599c2ffa08158088b2</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>6a1dec628ebbf7eaf702f172</t>
@@ -13004,7 +13340,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -13050,8 +13390,16 @@
       <c r="BH7" s="3" t="inlineStr"/>
       <c r="BI7" s="3" t="inlineStr"/>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -13300,13 +13648,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -13359,7 +13711,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>979c6de56e88420d8ca1a04da3a5cdd8</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>7650266cac8eba7e01b625f6</t>
@@ -13380,7 +13736,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -13426,8 +13786,16 @@
       <c r="BH9" s="3" t="inlineStr"/>
       <c r="BI9" s="3" t="inlineStr"/>
       <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -13478,13 +13846,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -13537,7 +13909,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>64c8938b9f384dfc8de6f04fe35535b2</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>1c43b4351d14ec3d18400653</t>
@@ -13558,7 +13934,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -13604,376 +13984,412 @@
       <c r="BH10" s="3" t="inlineStr"/>
       <c r="BI10" s="3" t="inlineStr"/>
       <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PNC</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>PNC Financial Services</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T01:07:33+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>PNC Financial Q3 Earnings Beat Estimates on Higher NII, Revenue Miss</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:01:40+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>$100M Equifax FCRA violations class action settlement</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.614</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWVlyMkJRTHp0emJNZTBFQnhlMDZMTTJJQTRJaGJVdjdma0NJQWNrdWhEUUVUYzllR3BobEoxNFpaTDJ0dG41Z01xMHBlbU4yVzhUUUlfMUpjNzVZWmtSTHZtYThMZ3YwRnNfSnpKX21NZmR2NEVYSi14em1iVlk5emxkemFKbHJWT1kzV1BJajdmLW5tRW5Ta0Q1bkRjT3BvRnJ0ZE9obFVVb1VKLU1KMF9ObVhUbzQzTU5taU01QVFtZVZr?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>Equifax FCRA 違規集體訴訟和解金額達 1 億美元</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>8db6f3649abe4d398280b8ab90bf2681</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>ada93744837e92947d202f3e</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>ec40275d5db2955cfa21f9e6</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLXVGVDNMaDZqNEpBMWgzY2dQeUQwdzBfZlBLbmhWXzZZMjllRnNRVC12RUlPRFJVNnhyMmJ1NG1PemwzRnMydTJHamZpaHlLVUpFQWpfMzJWNWFVcnRHaWo4LUVDVjROYUdUNE0yTy1RdFpkS3dVWHJYNjhKQVZPak9iODA4OXBVaUlIWHBKRzJ5VmJTc3hPODJjalNmdEhZLUttejI1Q1c0SWdt?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Zacks Investment Research</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>PNC Financial 第三季獲利超出預期，因 NII 較高，營收未達預期</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>revenue miss</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>9505b0aa170859877a0ab133</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>2587e39ff2aa09c9878f3293</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>PNC</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16T01:01:40+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>$100M Equifax FCRA violations class action settlement</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave, Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:52:16+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>CoreWeave credit default swaps hit distress levels as investors sour on AI debt</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>CDS利差擴大／信用風險升高</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.614</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>'-0.942</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWVlyMkJRTHp0emJNZTBFQnhlMDZMTTJJQTRJaGJVdjdma0NJQWNrdWhEUUVUYzllR3BobEoxNFpaTDJ0dG41Z01xMHBlbU4yVzhUUUlfMUpjNzVZWmtSTHZtYThMZ3YwRnNfSnpKX21NZmR2NEVYSi14em1iVlk5emxkemFKbHJWT1kzV1BJajdmLW5tRW5Ta0Q1bkRjT3BvRnJ0ZE9obFVVb1VKLU1KMF9ObVhUbzQzTU5taU01QVFtZVZr?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>Equifax FCRA 違規集體訴訟和解金額達 1 億美元</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>8db6f3649abe4d398280b8ab90bf2681</t>
-        </is>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>ada93744837e92947d202f3e</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>ec40275d5db2955cfa21f9e6</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>CDS_SPREAD_WIDENING</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>9a2cf57383d049b595007302e6da1711</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>15701a5080a3de1ba6257ef1</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>0040b1fc371664e2cde9c86e</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG12" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr">
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="4" t="inlineStr">
+      <c r="BL12" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -13992,22 +14408,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Zoetis Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16T00:54:05+08:00</t>
+          <t>2026-10-16T00:04:05+08:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>PNC posts strong Q3 EPS of $5.09, beating estimates despite slight revenue miss.</t>
+          <t>Zoetis (ZTS) Hit by Guidance Cuts, Met with Market Shrug</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -14018,7 +14434,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>財測下修</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -14028,13 +14444,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -14044,7 +14464,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>'-0.461</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
@@ -14058,17 +14478,17 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeFhEN2xkdjgyb0U1cjcwZ3NBVkRwaG5EQzU4aEFBdFlwV0FrbXdESHpBVXpvbmdad1BObDItekdKX2ppeVp1bG93WE81MVhDemdzcy1IX2pwNlptcWVabVZOSENNaDV4bFR4LWtlaDM4Q0tXWVptZ0JZYlJxNkxDXzR6aFFpem9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnVrVExqQ0pNWmhOR2U1VkZMVFpVMFFrZV9tVFloa1Bub3NnQnRSRGc2ME5icmt5SXNxNXRhT2VjRE5JdGlkLWxsRWNLbWV1SENjYUYzNEN2UE5GSnhqQXV4aXNINVdFV2Vyb3RrYTlCZks2MFhmU0U4Z01xaVhQeGM1bGN6QW5PVm9neXNJclFaUlE?oc=5</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>PNC 第三季每股收益強勁，達到 5.09 美元，儘管收入略有下降，但仍超出預期。</t>
+          <t>Zoetis (ZTS) 受到指導性下調的打擊，市場對此不以為然</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -14078,24 +14498,28 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>EARNINGS_WARNING</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>revenue miss</t>
+          <t>guidance cut</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>f7f3806f53354a81a6835571d4ca8e53</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>6a2633ad31b6c50e33125bed</t>
+          <t>9f004fe961a36687ee0eb7c3</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>d7a7e70cfcdca5486b0593a1</t>
+          <t>7512ff6d3ceb5edadd9ce246</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr"/>
@@ -14108,7 +14532,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -14116,14 +14544,18 @@
       <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="inlineStr"/>
       <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX13" s="3" t="inlineStr"/>
       <c r="AY13" s="3" t="inlineStr"/>
       <c r="AZ13" s="3" t="inlineStr"/>
       <c r="BA13" s="3" t="inlineStr"/>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="BC13" s="3" t="inlineStr">
@@ -14134,569 +14566,35 @@
       <c r="BD13" s="3" t="inlineStr"/>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF13" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG13" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
       <c r="BI13" s="3" t="inlineStr"/>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>CoreWeave, Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:52:16+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>CoreWeave credit default swaps hit distress levels as investors sour on AI debt</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>CDS利差擴大／信用風險升高</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONTRhRFpGVUE0Xy1YMnh5WHA3ZnFVZllZR3BHODhQaktaU1JGbHIzMElHZThsQTlESWZGNm9MRWllTzN0N01pTjNtTng2bmlqZmZFNmNaWlR4ZzVtUl93NV9VLW52b29vVjk3ZkNpa2ExWU9IVV9OTEx5MDhnNkdSaWNUcmI5TEU0cmNfSFNpTGx4YVR3NkJKVDZfdUFuMEFIX1p4X3lzM0M4RThWVngyclhaMXdSUmPSAbwBQVVfeXFMT1NTdnNpMGkzZldiaWV0eFk4MkliMHQxQzZCdkFvdjJ2bGdNYkNPeURkYTZ4VVBYcVpBV3dVVDJpb2xva240bWRpZ1g4QktNaUJtOWVwUUp5WUxZZXpnOGFrNFdzOUZab1ZVT3dnWlUxTlp0ZWZEeDY5YVE5SHNmRnZRNDlFU2NzTFg4YWpOaHhValdVMnJmVVNHa051UjZEZm5uaV9rQnZtWUNpcVRXRmVVUENKZE80YWtPTzI?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>CDS_SPREAD_WIDENING</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>9a2cf57383d049b595007302e6da1711</t>
-        </is>
-      </c>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>15701a5080a3de1ba6257ef1</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>0040b1fc371664e2cde9c86e</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr">
-        <is>
-          <t>Action|Event_Code|Level|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr">
+      <c r="BK13" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:13:28+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Fastenal Flashes Bullish Signal as Uptrend Holds Despite Margin Pressure</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWDFrVktXTms4Yk9Edk5VaDlIQ3pQVENZb29UclljTnlubExOTWFNV1ZOVEQwUEVqOEVRQUxuVGVfcTRmaU9CRTdOd2tweGhSR1E0N0xnNHlpZy1XelVSRU00cTNsNXRRRnZOR1lwVk9JMEkwSk95YlFZVlh4Q2NqSEp6blhoR1ZGclZ5MkFnam0tbjhwY2tVSzJzbUtfWUd2NVJpcmlXcmtIWDhsamc?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>儘管利潤率面臨壓力，但仍保持上升趨勢，Fastenal 閃爍看漲訊號</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>f5e0ef07093c7b595505d4a8</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>6decca22cb7377dd62f5f73e</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>ZTS</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:04:05+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis (ZTS) Hit by Guidance Cuts, Met with Market Shrug</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>'-0.461</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnVrVExqQ0pNWmhOR2U1VkZMVFpVMFFrZV9tVFloa1Bub3NnQnRSRGc2ME5icmt5SXNxNXRhT2VjRE5JdGlkLWxsRWNLbWV1SENjYUYzNEN2UE5GSnhqQXV4aXNINVdFV2Vyb3RrYTlCZks2MFhmU0U4Z01xaVhQeGM1bGN6QW5PVm9neXNJclFaUlE?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>Zoetis (ZTS) 受到指導性下調的打擊，市場對此不以為然</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>guidance cut</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
-        <is>
-          <t>9f004fe961a36687ee0eb7c3</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>7512ff6d3ceb5edadd9ce246</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
-        <is>
-          <t>ZTS</t>
-        </is>
-      </c>
-      <c r="BC16" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL16"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14707,7 +14605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15098,186 +14996,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>United Airlines Holdings</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:29:11+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Earnings Preview: United Airlines Stock Vulnerable to Downgrades</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.942</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPODQ4M05kLXhSb0ZUYXE1SGU0RlQ1X2dzazN3LVV2azY4dkJpUHFITlQtbDVfWldnQnhya181NDZHalVjQVhsSWxfQXZXWWNlUTBvZ0luQnVnZUN0TnZxRVE3X21iTE9KOGtpZWowRjA0ZEdNOFpWR1FTeENZTWVuaEtsZ0ctZVVUa2lkMVBRZnVjUDQ5aWd2eWNRbmVyWkZUWndCdHpKQndxN0NidDhMQXJGZjl4Rk41bFpHa2RJeVBrQUFY?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Schaeffer's Investment Research</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>收益預覽：聯合航空股票可能降級</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>downgrade</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>772d4856366ece14d22e6307</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>50881488da11b55253590b21</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>UAL</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-16.xlsx
+++ b/news_daily/2026-10-16.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>63626601e50d49f39f741439af93e31f</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>099e2edea607b3d926429fc0</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1066,28 +1090,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1131,7 +1159,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1140,7 +1168,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>88b416a0a0a84b768426f74a488e6a38</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>d719205b29084959c8916e08</t>
@@ -1161,7 +1193,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1197,10 +1233,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1236,28 +1284,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1301,7 +1353,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1310,7 +1362,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>738cae9c258e417c93a325b6261ee20f</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>8989721f0dca33ea572446b5</t>
@@ -1331,7 +1387,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1375,10 +1435,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1414,28 +1486,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1479,7 +1555,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1488,7 +1564,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>594ebd097c724f3d999909c1972a74f1</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>87657856a1e078f22bde44e7</t>
@@ -1509,7 +1589,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1553,10 +1637,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1592,28 +1688,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1657,7 +1757,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1666,7 +1766,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>92ccd45da90543f380697affb10e6a0f</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>dae4b5fa5644b028c7b0811a</t>
@@ -1687,7 +1791,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1731,10 +1839,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1770,28 +1890,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1835,7 +1959,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1844,7 +1968,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>ee0c37e9ada6462ebaa45dffce416e38</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>24cb51edf1c6d8476dd5602c</t>
@@ -1865,7 +1993,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1901,10 +2033,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1940,28 +2084,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2005,7 +2153,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2014,7 +2162,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>8664c3a4f51c4af283924f94b966e7b3</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>a84ca27414b8a3e6b3f6bc0c</t>
@@ -2035,7 +2187,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2071,10 +2227,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2110,28 +2278,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2175,7 +2347,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2184,7 +2356,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>2c5ed2c65ae44342a0b9bc067623e12e</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>2c139d5484417b2e0018f7fc</t>
@@ -2205,7 +2381,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2249,10 +2429,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2303,13 +2495,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2362,7 +2558,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>00c9e1ac05404401ae2a500b87496bd0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>3f1a7bb8df7ee00187402f05</t>
@@ -2383,7 +2583,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2429,8 +2633,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2481,13 +2693,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2540,7 +2756,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>dd5ece02c904434d8d37b49f1eeb00cb</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>0d5e36c2780ef72da60c9692</t>
@@ -2561,7 +2781,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2599,8 +2823,16 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2651,13 +2883,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2710,7 +2946,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>eb62128bcedc42ceb47dd33957e29916</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>1bf85c62ba5532b76a3e7fbf</t>
@@ -2731,7 +2971,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2777,8 +3021,16 @@
       <c r="BH12" s="2" t="inlineStr"/>
       <c r="BI12" s="2" t="inlineStr"/>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2829,13 +3081,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2888,7 +3144,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>fd23a007111c4905b630eeacea1c517a</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>5ac6ad14874e3fa36d2a8ef1</t>
@@ -2909,7 +3169,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -2947,8 +3211,16 @@
       <c r="BH13" s="2" t="inlineStr"/>
       <c r="BI13" s="2" t="inlineStr"/>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2984,28 +3256,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3049,7 +3325,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3058,7 +3334,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>a7bfcf60baf141ecb1e493571d9df718</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>1f797709bf32f3e4e7711143</t>
@@ -3079,7 +3359,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3123,10 +3407,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3360,28 +3656,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3425,7 +3725,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3434,7 +3734,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>08d6d7ea62384715bb207473250816a6</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>0f2506253d509e65dfafc47c</t>
@@ -3455,7 +3759,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3499,10 +3807,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3538,28 +3858,32 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3603,7 +3927,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3612,7 +3936,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>6eebabca2d76437eb7b97d3c59505eba</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>230fc14afd40fa701d659dc4</t>
@@ -3633,7 +3961,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3677,10 +4009,22 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3716,28 +4060,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3781,7 +4129,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3790,7 +4138,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>0ad02c16fb584f5fa8adb4a3295eb2aa</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>86d511f2cb8dae5c92ca0d29</t>
@@ -3811,7 +4163,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -3847,10 +4203,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3886,28 +4254,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3951,7 +4323,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -3960,7 +4332,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>5cfb7c9c692d4a43a957f28fa6abb854</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>f338067f9944282671adda9d</t>
@@ -3981,7 +4357,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4017,10 +4397,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4056,28 +4448,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4121,7 +4517,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4130,7 +4526,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>ac14af575fef4ae6a0acb38eeaf2fb10</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>23e539f721ea2238bca8986c</t>
@@ -4151,7 +4551,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4195,10 +4599,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4234,28 +4650,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4299,7 +4719,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4308,7 +4728,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>bb8bbde0d60d40b08f560625b22c36be</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>1f28d5dae095a8de524655b3</t>
@@ -4329,7 +4753,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4373,10 +4801,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4808,28 +5248,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4873,7 +5317,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -4882,7 +5326,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>aee6f058befa457c91b7d56eabc4e819</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>aab161f99091a12267a49454</t>
@@ -4903,7 +5351,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -4947,10 +5399,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4986,28 +5450,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5051,7 +5519,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5060,7 +5528,11 @@
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0792156bb85642e9a1f7d96499207c6a</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>61dabbd3f9550b501ce52dc4</t>
@@ -5081,7 +5553,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5117,10 +5593,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5156,28 +5644,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5221,7 +5713,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5230,7 +5722,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>76db5256b4f445fdb03bd74d941b7577</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>b49e6b504f0164e1a32cb10f</t>
@@ -5251,7 +5747,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5295,10 +5795,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -5547,13 +6059,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5606,7 +6122,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>6b4a5da46637446c98754fd55218cbe2</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>bfa0db7ea7b5b97e278817b1</t>
@@ -5627,7 +6147,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -5665,8 +6189,16 @@
       <c r="BH28" s="2" t="inlineStr"/>
       <c r="BI28" s="2" t="inlineStr"/>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5717,13 +6249,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5776,7 +6312,11 @@
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>d3fc69888fc549dca220bc9894ea9e46</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>354f7b133c2d32e709321111</t>
@@ -5797,7 +6337,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -5835,8 +6379,16 @@
       <c r="BH29" s="2" t="inlineStr"/>
       <c r="BI29" s="2" t="inlineStr"/>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5887,13 +6439,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5946,7 +6502,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>ec5df93c460a45c694f21032c3aef57e</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>fe29664746f5c269621f3319</t>
@@ -5967,7 +6527,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6013,8 +6577,16 @@
       <c r="BH30" s="2" t="inlineStr"/>
       <c r="BI30" s="2" t="inlineStr"/>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6050,28 +6622,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6111,7 +6687,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6120,7 +6696,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>97268c44bbae48f1ba191a3c56f3485b</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>1f4066e896eaba7e15a82343</t>
@@ -6141,7 +6721,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6185,10 +6769,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6414,28 +7010,32 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6479,7 +7079,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -6488,7 +7088,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>4d1c2c32ddc34c8d8dbcfa31d93ec857</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>89b25980312decf52d1133f6</t>
@@ -6509,7 +7113,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6545,10 +7153,22 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
-      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6584,28 +7204,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6649,7 +7273,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6658,7 +7282,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>18656ef6bd254dacbc379fb5a7f28a2b</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>44114de3a97f9c438fdef1ba</t>
@@ -6679,7 +7307,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -6723,10 +7355,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6777,13 +7421,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6836,7 +7484,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>3f8f9ecf37204707aa7a2ca4b02ccc48</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>8126b38924b24d49a23f0043</t>
@@ -6857,7 +7509,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -6895,8 +7551,16 @@
       <c r="BH35" s="2" t="inlineStr"/>
       <c r="BI35" s="2" t="inlineStr"/>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7545,13 +8209,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7604,7 +8272,11 @@
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr"/>
-      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>8b8985c558bf4d8b8af064663109a06f</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>e8ca40f96f7d26dcff5fa0b1</t>
@@ -7625,7 +8297,11 @@
       <c r="AL39" s="2" t="inlineStr"/>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
-      <c r="AO39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="2" t="inlineStr"/>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -7671,8 +8347,16 @@
       <c r="BH39" s="2" t="inlineStr"/>
       <c r="BI39" s="2" t="inlineStr"/>
       <c r="BJ39" s="2" t="inlineStr"/>
-      <c r="BK39" s="2" t="inlineStr"/>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7910,28 +8594,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7975,7 +8663,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -7984,7 +8672,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>d9e0fceae68441f78e0e1c4ffbef79c2</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>cec953949e4b8b663ccbdda0</t>
@@ -8005,7 +8697,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8049,10 +8745,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8088,28 +8796,32 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -8153,7 +8865,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -8162,7 +8874,11 @@
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr"/>
-      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>7f5b2063a0c44fd6a182a6a31f544f7e</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>41a8f3996c269dcb6b02d58c</t>
@@ -8183,7 +8899,11 @@
       <c r="AL42" s="2" t="inlineStr"/>
       <c r="AM42" s="2" t="inlineStr"/>
       <c r="AN42" s="2" t="inlineStr"/>
-      <c r="AO42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP42" s="2" t="inlineStr"/>
       <c r="AQ42" s="2" t="inlineStr"/>
       <c r="AR42" s="2" t="inlineStr"/>
@@ -8227,10 +8947,22 @@
         </is>
       </c>
       <c r="BH42" s="2" t="inlineStr"/>
-      <c r="BI42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ42" s="2" t="inlineStr"/>
-      <c r="BK42" s="2" t="inlineStr"/>
-      <c r="BL42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -9073,13 +9805,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -9132,7 +9868,11 @@
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr"/>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>d11ccfb106cb42c982ed1b76233a6311</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>86d8879e16208cc8696b928a</t>
@@ -9153,7 +9893,11 @@
       <c r="AL47" s="2" t="inlineStr"/>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
-      <c r="AO47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP47" s="2" t="inlineStr"/>
       <c r="AQ47" s="2" t="inlineStr"/>
       <c r="AR47" s="2" t="inlineStr"/>
@@ -9199,8 +9943,16 @@
       <c r="BH47" s="2" t="inlineStr"/>
       <c r="BI47" s="2" t="inlineStr"/>
       <c r="BJ47" s="2" t="inlineStr"/>
-      <c r="BK47" s="2" t="inlineStr"/>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9628,28 +10380,32 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -9693,7 +10449,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -9702,7 +10458,11 @@
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr"/>
-      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>5dbcb93e80f3415a882e71320de0dc8e</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>df298e6a49529021780cba95</t>
@@ -9723,7 +10483,11 @@
       <c r="AL50" s="2" t="inlineStr"/>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP50" s="2" t="inlineStr"/>
       <c r="AQ50" s="2" t="inlineStr"/>
       <c r="AR50" s="2" t="inlineStr"/>
@@ -9767,10 +10531,22 @@
         </is>
       </c>
       <c r="BH50" s="2" t="inlineStr"/>
-      <c r="BI50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ50" s="2" t="inlineStr"/>
-      <c r="BK50" s="2" t="inlineStr"/>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -10217,13 +10993,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10276,7 +11056,11 @@
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr"/>
-      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>db9b1dd71c594400a2add33e34f6022d</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>3173ac3803b340c30d54d682</t>
@@ -10297,7 +11081,11 @@
       <c r="AL53" s="2" t="inlineStr"/>
       <c r="AM53" s="2" t="inlineStr"/>
       <c r="AN53" s="2" t="inlineStr"/>
-      <c r="AO53" s="2" t="inlineStr"/>
+      <c r="AO53" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP53" s="2" t="inlineStr"/>
       <c r="AQ53" s="2" t="inlineStr"/>
       <c r="AR53" s="2" t="inlineStr"/>
@@ -10343,8 +11131,16 @@
       <c r="BH53" s="2" t="inlineStr"/>
       <c r="BI53" s="2" t="inlineStr"/>
       <c r="BJ53" s="2" t="inlineStr"/>
-      <c r="BK53" s="2" t="inlineStr"/>
-      <c r="BL53" s="2" t="inlineStr"/>
+      <c r="BK53" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10597,13 +11393,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -10656,7 +11456,11 @@
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr"/>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>cf827ccf953b42a3afbf0b6cd42c0354</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>b0248da7fecda4bb878fa326</t>
@@ -10677,7 +11481,11 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr"/>
       <c r="AN55" s="2" t="inlineStr"/>
-      <c r="AO55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="2" t="inlineStr"/>
       <c r="AQ55" s="2" t="inlineStr"/>
       <c r="AR55" s="2" t="inlineStr"/>
@@ -10715,8 +11523,16 @@
       <c r="BH55" s="2" t="inlineStr"/>
       <c r="BI55" s="2" t="inlineStr"/>
       <c r="BJ55" s="2" t="inlineStr"/>
-      <c r="BK55" s="2" t="inlineStr"/>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10767,13 +11583,17 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -10826,7 +11646,11 @@
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr"/>
-      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>21edcba3724048e7bc949cb57695eb6a</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>1075dadae9636acb6ad75ead</t>
@@ -10847,7 +11671,11 @@
       <c r="AL56" s="2" t="inlineStr"/>
       <c r="AM56" s="2" t="inlineStr"/>
       <c r="AN56" s="2" t="inlineStr"/>
-      <c r="AO56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP56" s="2" t="inlineStr"/>
       <c r="AQ56" s="2" t="inlineStr"/>
       <c r="AR56" s="2" t="inlineStr"/>
@@ -10893,8 +11721,16 @@
       <c r="BH56" s="2" t="inlineStr"/>
       <c r="BI56" s="2" t="inlineStr"/>
       <c r="BJ56" s="2" t="inlineStr"/>
-      <c r="BK56" s="2" t="inlineStr"/>
-      <c r="BL56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10945,13 +11781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -11004,7 +11844,11 @@
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr"/>
-      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>5a8209cb2b514c07a5f642838970badb</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>3c1db0cd1db83ac0ded76f33</t>
@@ -11025,7 +11869,11 @@
       <c r="AL57" s="2" t="inlineStr"/>
       <c r="AM57" s="2" t="inlineStr"/>
       <c r="AN57" s="2" t="inlineStr"/>
-      <c r="AO57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="2" t="inlineStr"/>
       <c r="AQ57" s="2" t="inlineStr"/>
       <c r="AR57" s="2" t="inlineStr"/>
@@ -11071,8 +11919,16 @@
       <c r="BH57" s="2" t="inlineStr"/>
       <c r="BI57" s="2" t="inlineStr"/>
       <c r="BJ57" s="2" t="inlineStr"/>
-      <c r="BK57" s="2" t="inlineStr"/>
-      <c r="BL57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11302,28 +12158,32 @@
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -11367,7 +12227,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -11376,7 +12236,11 @@
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr"/>
-      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>f334344a8e724f80b68e520abbc7d5a7</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>90b1da9d242fa3dd26274541</t>
@@ -11397,7 +12261,11 @@
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr"/>
       <c r="AN59" s="2" t="inlineStr"/>
-      <c r="AO59" s="2" t="inlineStr"/>
+      <c r="AO59" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP59" s="2" t="inlineStr"/>
       <c r="AQ59" s="2" t="inlineStr"/>
       <c r="AR59" s="2" t="inlineStr"/>
@@ -11441,10 +12309,22 @@
         </is>
       </c>
       <c r="BH59" s="2" t="inlineStr"/>
-      <c r="BI59" s="2" t="inlineStr"/>
+      <c r="BI59" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ59" s="2" t="inlineStr"/>
-      <c r="BK59" s="2" t="inlineStr"/>
-      <c r="BL59" s="2" t="inlineStr"/>
+      <c r="BK59" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -11693,13 +12573,17 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -11748,7 +12632,11 @@
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr"/>
-      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>c0c2d7fbddb0485891816afce6dc942e</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>98b3b84d1a6d82f4ed97e1fe</t>
@@ -11769,7 +12657,11 @@
       <c r="AL61" s="2" t="inlineStr"/>
       <c r="AM61" s="2" t="inlineStr"/>
       <c r="AN61" s="2" t="inlineStr"/>
-      <c r="AO61" s="2" t="inlineStr"/>
+      <c r="AO61" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP61" s="2" t="inlineStr"/>
       <c r="AQ61" s="2" t="inlineStr"/>
       <c r="AR61" s="2" t="inlineStr"/>
@@ -11815,8 +12707,16 @@
       <c r="BH61" s="2" t="inlineStr"/>
       <c r="BI61" s="2" t="inlineStr"/>
       <c r="BJ61" s="2" t="inlineStr"/>
-      <c r="BK61" s="2" t="inlineStr"/>
-      <c r="BL61" s="2" t="inlineStr"/>
+      <c r="BK61" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL61"/>
